--- a/data/catalogo_productos.xlsx
+++ b/data/catalogo_productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://manpowergroupapps-my.sharepoint.com/personal/andres_betancury_manpowergroup_com_co/Documents/1. Proyectos/Cientifico de datos/Pruebas y ejemplos/dk/Mimitos/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_05A231AE924C45E89FBA9C1BDB1CCF0AD6CEE74D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF9AD8CC-22FB-41FD-B8C1-15CA309FB675}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_05A231AE924C45E89FBA9C1BDB1CCF0AD6CEE74D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{789A29C0-D6B3-4766-B7AA-5BE7FDD50FBA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1288,6 +1288,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="13.54296875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">

--- a/data/catalogo_productos.xlsx
+++ b/data/catalogo_productos.xlsx
@@ -1,26 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://manpowergroupapps-my.sharepoint.com/personal/andres_betancury_manpowergroup_com_co/Documents/1. Proyectos/Cientifico de datos/Pruebas y ejemplos/dk/Mimitos/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mpgcobetancurca\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_05A231AE924C45E89FBA9C1BDB1CCF0AD6CEE74D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{789A29C0-D6B3-4766-B7AA-5BE7FDD50FBA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8AA8E4-C88C-4483-9A07-9215AE2460BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="652">
   <si>
     <t>img</t>
   </si>
@@ -947,14 +961,1057 @@
   </si>
   <si>
     <t>didacticos</t>
+  </si>
+  <si>
+    <t>coleccionables</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca1.png</t>
+  </si>
+  <si>
+    <t>Coleccionable</t>
+  </si>
+  <si>
+    <t>Figura coleccionable de alta calidad, diseñada con gran nivel de detalle y acabados premium. Ideal para exhibición, combina estilo, personalidad y elementos únicos que la convierten en una pieza especial para cualquier colección</t>
+  </si>
+  <si>
+    <t>Regalo, Cumpleaños, Aficcionados de colección</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca2.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca3.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca4.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca5.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca6.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca7.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca8.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca9.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca10.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca11.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca12.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca13.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca14.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca15.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca16.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca17.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca18.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca19.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca20.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca21.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca22.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca23.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca24.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca25.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca26.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca27.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca28.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca29.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca30.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca31.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca32.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca33.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca34.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca35.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca36.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca37.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca38.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca39.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca40.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca41.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca42.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca43.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca44.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca45.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca46.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca47.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca48.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca49.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca50.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca51.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca52.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca53.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca54.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca55.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca56.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca57.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca58.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca59.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca60.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca61.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca62.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca63.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca64.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca65.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca66.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca67.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca68.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca69.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca70.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca71.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca72.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca73.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca74.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca75.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca76.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca77.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca78.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca79.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca80.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca81.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca82.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca83.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca84.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca85.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca86.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca87.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca88.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca89.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca90.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca91.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca92.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca93.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca94.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca95.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca96.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca97.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca98.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca99.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca100.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca101.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca102.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca103.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca104.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca105.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca106.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca107.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca108.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca109.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca110.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca111.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca112.png</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca113.png</t>
+  </si>
+  <si>
+    <t>21 × 20 cm</t>
+  </si>
+  <si>
+    <t>22 × 20 cm</t>
+  </si>
+  <si>
+    <t>23 × 20 cm</t>
+  </si>
+  <si>
+    <t>24 × 20 cm</t>
+  </si>
+  <si>
+    <t>26 × 20 cm</t>
+  </si>
+  <si>
+    <t>27 × 20 cm</t>
+  </si>
+  <si>
+    <t>28 × 20 cm</t>
+  </si>
+  <si>
+    <t>29 × 20 cm</t>
+  </si>
+  <si>
+    <t>30 × 20 cm</t>
+  </si>
+  <si>
+    <t>31 × 20 cm</t>
+  </si>
+  <si>
+    <t>32 × 20 cm</t>
+  </si>
+  <si>
+    <t>33 × 20 cm</t>
+  </si>
+  <si>
+    <t>34 × 20 cm</t>
+  </si>
+  <si>
+    <t>35 × 20 cm</t>
+  </si>
+  <si>
+    <t>36 × 20 cm</t>
+  </si>
+  <si>
+    <t>37 × 20 cm</t>
+  </si>
+  <si>
+    <t>38 × 20 cm</t>
+  </si>
+  <si>
+    <t>39 × 20 cm</t>
+  </si>
+  <si>
+    <t>40 × 20 cm</t>
+  </si>
+  <si>
+    <t>41 × 20 cm</t>
+  </si>
+  <si>
+    <t>42 × 20 cm</t>
+  </si>
+  <si>
+    <t>43 × 20 cm</t>
+  </si>
+  <si>
+    <t>44 × 20 cm</t>
+  </si>
+  <si>
+    <t>45 × 20 cm</t>
+  </si>
+  <si>
+    <t>46 × 20 cm</t>
+  </si>
+  <si>
+    <t>47 × 20 cm</t>
+  </si>
+  <si>
+    <t>48 × 20 cm</t>
+  </si>
+  <si>
+    <t>49 × 20 cm</t>
+  </si>
+  <si>
+    <t>50 × 20 cm</t>
+  </si>
+  <si>
+    <t>51 × 20 cm</t>
+  </si>
+  <si>
+    <t>52 × 20 cm</t>
+  </si>
+  <si>
+    <t>53 × 20 cm</t>
+  </si>
+  <si>
+    <t>54 × 20 cm</t>
+  </si>
+  <si>
+    <t>55 × 20 cm</t>
+  </si>
+  <si>
+    <t>56 × 20 cm</t>
+  </si>
+  <si>
+    <t>57 × 20 cm</t>
+  </si>
+  <si>
+    <t>58 × 20 cm</t>
+  </si>
+  <si>
+    <t>59 × 20 cm</t>
+  </si>
+  <si>
+    <t>60 × 20 cm</t>
+  </si>
+  <si>
+    <t>61 × 20 cm</t>
+  </si>
+  <si>
+    <t>62 × 20 cm</t>
+  </si>
+  <si>
+    <t>63 × 20 cm</t>
+  </si>
+  <si>
+    <t>64 × 20 cm</t>
+  </si>
+  <si>
+    <t>65 × 20 cm</t>
+  </si>
+  <si>
+    <t>66 × 20 cm</t>
+  </si>
+  <si>
+    <t>67 × 20 cm</t>
+  </si>
+  <si>
+    <t>68 × 20 cm</t>
+  </si>
+  <si>
+    <t>69 × 20 cm</t>
+  </si>
+  <si>
+    <t>70 × 20 cm</t>
+  </si>
+  <si>
+    <t>71 × 20 cm</t>
+  </si>
+  <si>
+    <t>72 × 20 cm</t>
+  </si>
+  <si>
+    <t>73 × 20 cm</t>
+  </si>
+  <si>
+    <t>74 × 20 cm</t>
+  </si>
+  <si>
+    <t>75 × 20 cm</t>
+  </si>
+  <si>
+    <t>76 × 20 cm</t>
+  </si>
+  <si>
+    <t>77 × 20 cm</t>
+  </si>
+  <si>
+    <t>78 × 20 cm</t>
+  </si>
+  <si>
+    <t>79 × 20 cm</t>
+  </si>
+  <si>
+    <t>80 × 20 cm</t>
+  </si>
+  <si>
+    <t>81 × 20 cm</t>
+  </si>
+  <si>
+    <t>82 × 20 cm</t>
+  </si>
+  <si>
+    <t>83 × 20 cm</t>
+  </si>
+  <si>
+    <t>84 × 20 cm</t>
+  </si>
+  <si>
+    <t>85 × 20 cm</t>
+  </si>
+  <si>
+    <t>86 × 20 cm</t>
+  </si>
+  <si>
+    <t>87 × 20 cm</t>
+  </si>
+  <si>
+    <t>88 × 20 cm</t>
+  </si>
+  <si>
+    <t>89 × 20 cm</t>
+  </si>
+  <si>
+    <t>90 × 20 cm</t>
+  </si>
+  <si>
+    <t>91 × 20 cm</t>
+  </si>
+  <si>
+    <t>92 × 20 cm</t>
+  </si>
+  <si>
+    <t>93 × 20 cm</t>
+  </si>
+  <si>
+    <t>94 × 20 cm</t>
+  </si>
+  <si>
+    <t>95 × 20 cm</t>
+  </si>
+  <si>
+    <t>96 × 20 cm</t>
+  </si>
+  <si>
+    <t>97 × 20 cm</t>
+  </si>
+  <si>
+    <t>98 × 20 cm</t>
+  </si>
+  <si>
+    <t>99 × 20 cm</t>
+  </si>
+  <si>
+    <t>100 × 20 cm</t>
+  </si>
+  <si>
+    <t>101 × 20 cm</t>
+  </si>
+  <si>
+    <t>102 × 20 cm</t>
+  </si>
+  <si>
+    <t>103 × 20 cm</t>
+  </si>
+  <si>
+    <t>104 × 20 cm</t>
+  </si>
+  <si>
+    <t>105 × 20 cm</t>
+  </si>
+  <si>
+    <t>106 × 20 cm</t>
+  </si>
+  <si>
+    <t>107 × 20 cm</t>
+  </si>
+  <si>
+    <t>108 × 20 cm</t>
+  </si>
+  <si>
+    <t>109 × 20 cm</t>
+  </si>
+  <si>
+    <t>110 × 20 cm</t>
+  </si>
+  <si>
+    <t>111 × 20 cm</t>
+  </si>
+  <si>
+    <t>112 × 20 cm</t>
+  </si>
+  <si>
+    <t>113 × 20 cm</t>
+  </si>
+  <si>
+    <t>114 × 20 cm</t>
+  </si>
+  <si>
+    <t>115 × 20 cm</t>
+  </si>
+  <si>
+    <t>116 × 20 cm</t>
+  </si>
+  <si>
+    <t>117 × 20 cm</t>
+  </si>
+  <si>
+    <t>118 × 20 cm</t>
+  </si>
+  <si>
+    <t>119 × 20 cm</t>
+  </si>
+  <si>
+    <t>120 × 20 cm</t>
+  </si>
+  <si>
+    <t>121 × 20 cm</t>
+  </si>
+  <si>
+    <t>122 × 20 cm</t>
+  </si>
+  <si>
+    <t>123 × 20 cm</t>
+  </si>
+  <si>
+    <t>124 × 20 cm</t>
+  </si>
+  <si>
+    <t>125 × 20 cm</t>
+  </si>
+  <si>
+    <t>126 × 20 cm</t>
+  </si>
+  <si>
+    <t>127 × 20 cm</t>
+  </si>
+  <si>
+    <t>128 × 20 cm</t>
+  </si>
+  <si>
+    <t>129 × 20 cm</t>
+  </si>
+  <si>
+    <t>130 × 20 cm</t>
+  </si>
+  <si>
+    <t>131 × 20 cm</t>
+  </si>
+  <si>
+    <t>132 × 20 cm</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca</t>
+  </si>
+  <si>
+    <t>.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca1.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca2.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca3.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca4.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca5.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca6.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca7.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca8.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca9.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca10.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca11.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca12.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca13.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca14.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca15.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca16.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca17.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca18.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca19.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca20.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca21.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca22.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca23.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca24.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca25.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca26.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca27.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca28.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca29.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca30.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca31.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca32.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca33.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca34.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca35.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca36.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca37.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca38.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca39.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca40.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca41.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca42.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca43.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca44.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca45.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca46.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca47.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca48.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca49.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca50.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca51.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca52.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca53.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca54.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca55.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca56.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca57.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca58.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca59.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca60.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca61.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca62.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca63.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca64.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca65.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca66.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca67.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca68.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca69.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca70.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca71.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca72.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca73.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca74.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca75.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca76.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca77.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca78.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca79.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca80.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca81.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca82.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca83.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca84.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca85.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca86.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca87.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca88.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca89.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca90.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca91.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca92.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca93.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca94.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca95.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca96.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca97.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca98.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca99.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca100.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca101.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca102.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca103.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca104.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca105.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca106.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca107.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca108.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca109.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca110.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca111.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca112.jpg</t>
+  </si>
+  <si>
+    <t>img/coleccionables/ca113.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -982,8 +2039,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1286,10 +2344,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J174"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.54296875" customWidth="1"/>
+    <col min="2" max="2" width="24.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -3118,7 +4176,5332 @@
         <v>304</v>
       </c>
     </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>309</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="C62" t="s">
+        <v>311</v>
+      </c>
+      <c r="D62">
+        <v>5000</v>
+      </c>
+      <c r="E62">
+        <v>10000</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="H62" t="s">
+        <v>312</v>
+      </c>
+      <c r="I62" t="s">
+        <v>298</v>
+      </c>
+      <c r="J62" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>309</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C63" t="s">
+        <v>311</v>
+      </c>
+      <c r="D63">
+        <v>5000</v>
+      </c>
+      <c r="E63">
+        <v>10000</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+      <c r="H63" t="s">
+        <v>312</v>
+      </c>
+      <c r="I63" t="s">
+        <v>426</v>
+      </c>
+      <c r="J63" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>309</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="C64" t="s">
+        <v>311</v>
+      </c>
+      <c r="D64">
+        <v>5000</v>
+      </c>
+      <c r="E64">
+        <v>10000</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="H64" t="s">
+        <v>312</v>
+      </c>
+      <c r="I64" t="s">
+        <v>427</v>
+      </c>
+      <c r="J64" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>309</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C65" t="s">
+        <v>311</v>
+      </c>
+      <c r="D65">
+        <v>5000</v>
+      </c>
+      <c r="E65">
+        <v>10000</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="H65" t="s">
+        <v>312</v>
+      </c>
+      <c r="I65" t="s">
+        <v>428</v>
+      </c>
+      <c r="J65" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>309</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C66" t="s">
+        <v>311</v>
+      </c>
+      <c r="D66">
+        <v>5000</v>
+      </c>
+      <c r="E66">
+        <v>10000</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="H66" t="s">
+        <v>312</v>
+      </c>
+      <c r="I66" t="s">
+        <v>429</v>
+      </c>
+      <c r="J66" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>309</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C67" t="s">
+        <v>311</v>
+      </c>
+      <c r="D67">
+        <v>5000</v>
+      </c>
+      <c r="E67">
+        <v>10000</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="H67" t="s">
+        <v>312</v>
+      </c>
+      <c r="I67" t="s">
+        <v>218</v>
+      </c>
+      <c r="J67" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>309</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C68" t="s">
+        <v>311</v>
+      </c>
+      <c r="D68">
+        <v>5000</v>
+      </c>
+      <c r="E68">
+        <v>10000</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="H68" t="s">
+        <v>312</v>
+      </c>
+      <c r="I68" t="s">
+        <v>430</v>
+      </c>
+      <c r="J68" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>309</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="C69" t="s">
+        <v>311</v>
+      </c>
+      <c r="D69">
+        <v>5000</v>
+      </c>
+      <c r="E69">
+        <v>10000</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
+      </c>
+      <c r="H69" t="s">
+        <v>312</v>
+      </c>
+      <c r="I69" t="s">
+        <v>431</v>
+      </c>
+      <c r="J69" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>309</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="C70" t="s">
+        <v>311</v>
+      </c>
+      <c r="D70">
+        <v>5000</v>
+      </c>
+      <c r="E70">
+        <v>10000</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="H70" t="s">
+        <v>312</v>
+      </c>
+      <c r="I70" t="s">
+        <v>432</v>
+      </c>
+      <c r="J70" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>309</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="C71" t="s">
+        <v>311</v>
+      </c>
+      <c r="D71">
+        <v>5000</v>
+      </c>
+      <c r="E71">
+        <v>10000</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="H71" t="s">
+        <v>312</v>
+      </c>
+      <c r="I71" t="s">
+        <v>433</v>
+      </c>
+      <c r="J71" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>309</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="C72" t="s">
+        <v>311</v>
+      </c>
+      <c r="D72">
+        <v>5000</v>
+      </c>
+      <c r="E72">
+        <v>10000</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="H72" t="s">
+        <v>312</v>
+      </c>
+      <c r="I72" t="s">
+        <v>434</v>
+      </c>
+      <c r="J72" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>309</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="C73" t="s">
+        <v>311</v>
+      </c>
+      <c r="D73">
+        <v>5000</v>
+      </c>
+      <c r="E73">
+        <v>10000</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="H73" t="s">
+        <v>312</v>
+      </c>
+      <c r="I73" t="s">
+        <v>435</v>
+      </c>
+      <c r="J73" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>309</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C74" t="s">
+        <v>311</v>
+      </c>
+      <c r="D74">
+        <v>5000</v>
+      </c>
+      <c r="E74">
+        <v>10000</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="H74" t="s">
+        <v>312</v>
+      </c>
+      <c r="I74" t="s">
+        <v>436</v>
+      </c>
+      <c r="J74" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>309</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="C75" t="s">
+        <v>311</v>
+      </c>
+      <c r="D75">
+        <v>5000</v>
+      </c>
+      <c r="E75">
+        <v>10000</v>
+      </c>
+      <c r="F75">
+        <v>1</v>
+      </c>
+      <c r="H75" t="s">
+        <v>312</v>
+      </c>
+      <c r="I75" t="s">
+        <v>437</v>
+      </c>
+      <c r="J75" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>309</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C76" t="s">
+        <v>311</v>
+      </c>
+      <c r="D76">
+        <v>5000</v>
+      </c>
+      <c r="E76">
+        <v>10000</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="H76" t="s">
+        <v>312</v>
+      </c>
+      <c r="I76" t="s">
+        <v>438</v>
+      </c>
+      <c r="J76" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>309</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="C77" t="s">
+        <v>311</v>
+      </c>
+      <c r="D77">
+        <v>5000</v>
+      </c>
+      <c r="E77">
+        <v>10000</v>
+      </c>
+      <c r="F77">
+        <v>1</v>
+      </c>
+      <c r="H77" t="s">
+        <v>312</v>
+      </c>
+      <c r="I77" t="s">
+        <v>439</v>
+      </c>
+      <c r="J77" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>309</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="C78" t="s">
+        <v>311</v>
+      </c>
+      <c r="D78">
+        <v>5000</v>
+      </c>
+      <c r="E78">
+        <v>10000</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="H78" t="s">
+        <v>312</v>
+      </c>
+      <c r="I78" t="s">
+        <v>440</v>
+      </c>
+      <c r="J78" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>309</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="C79" t="s">
+        <v>311</v>
+      </c>
+      <c r="D79">
+        <v>5000</v>
+      </c>
+      <c r="E79">
+        <v>10000</v>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+      <c r="H79" t="s">
+        <v>312</v>
+      </c>
+      <c r="I79" t="s">
+        <v>441</v>
+      </c>
+      <c r="J79" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>309</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="C80" t="s">
+        <v>311</v>
+      </c>
+      <c r="D80">
+        <v>5000</v>
+      </c>
+      <c r="E80">
+        <v>10000</v>
+      </c>
+      <c r="F80">
+        <v>1</v>
+      </c>
+      <c r="H80" t="s">
+        <v>312</v>
+      </c>
+      <c r="I80" t="s">
+        <v>442</v>
+      </c>
+      <c r="J80" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>309</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C81" t="s">
+        <v>311</v>
+      </c>
+      <c r="D81">
+        <v>5000</v>
+      </c>
+      <c r="E81">
+        <v>10000</v>
+      </c>
+      <c r="F81">
+        <v>1</v>
+      </c>
+      <c r="H81" t="s">
+        <v>312</v>
+      </c>
+      <c r="I81" t="s">
+        <v>443</v>
+      </c>
+      <c r="J81" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>309</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C82" t="s">
+        <v>311</v>
+      </c>
+      <c r="D82">
+        <v>5000</v>
+      </c>
+      <c r="E82">
+        <v>10000</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="H82" t="s">
+        <v>312</v>
+      </c>
+      <c r="I82" t="s">
+        <v>444</v>
+      </c>
+      <c r="J82" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>309</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="C83" t="s">
+        <v>311</v>
+      </c>
+      <c r="D83">
+        <v>5000</v>
+      </c>
+      <c r="E83">
+        <v>10000</v>
+      </c>
+      <c r="F83">
+        <v>1</v>
+      </c>
+      <c r="H83" t="s">
+        <v>312</v>
+      </c>
+      <c r="I83" t="s">
+        <v>445</v>
+      </c>
+      <c r="J83" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>309</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="C84" t="s">
+        <v>311</v>
+      </c>
+      <c r="D84">
+        <v>5000</v>
+      </c>
+      <c r="E84">
+        <v>10000</v>
+      </c>
+      <c r="F84">
+        <v>1</v>
+      </c>
+      <c r="H84" t="s">
+        <v>312</v>
+      </c>
+      <c r="I84" t="s">
+        <v>446</v>
+      </c>
+      <c r="J84" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>309</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="C85" t="s">
+        <v>311</v>
+      </c>
+      <c r="D85">
+        <v>5000</v>
+      </c>
+      <c r="E85">
+        <v>10000</v>
+      </c>
+      <c r="F85">
+        <v>1</v>
+      </c>
+      <c r="H85" t="s">
+        <v>312</v>
+      </c>
+      <c r="I85" t="s">
+        <v>447</v>
+      </c>
+      <c r="J85" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>309</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="C86" t="s">
+        <v>311</v>
+      </c>
+      <c r="D86">
+        <v>5000</v>
+      </c>
+      <c r="E86">
+        <v>10000</v>
+      </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
+      <c r="H86" t="s">
+        <v>312</v>
+      </c>
+      <c r="I86" t="s">
+        <v>448</v>
+      </c>
+      <c r="J86" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>309</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="C87" t="s">
+        <v>311</v>
+      </c>
+      <c r="D87">
+        <v>5000</v>
+      </c>
+      <c r="E87">
+        <v>10000</v>
+      </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
+      <c r="H87" t="s">
+        <v>312</v>
+      </c>
+      <c r="I87" t="s">
+        <v>449</v>
+      </c>
+      <c r="J87" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>309</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="C88" t="s">
+        <v>311</v>
+      </c>
+      <c r="D88">
+        <v>5000</v>
+      </c>
+      <c r="E88">
+        <v>10000</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="H88" t="s">
+        <v>312</v>
+      </c>
+      <c r="I88" t="s">
+        <v>450</v>
+      </c>
+      <c r="J88" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>309</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="C89" t="s">
+        <v>311</v>
+      </c>
+      <c r="D89">
+        <v>5000</v>
+      </c>
+      <c r="E89">
+        <v>10000</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="H89" t="s">
+        <v>312</v>
+      </c>
+      <c r="I89" t="s">
+        <v>451</v>
+      </c>
+      <c r="J89" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>309</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="C90" t="s">
+        <v>311</v>
+      </c>
+      <c r="D90">
+        <v>5000</v>
+      </c>
+      <c r="E90">
+        <v>10000</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="H90" t="s">
+        <v>312</v>
+      </c>
+      <c r="I90" t="s">
+        <v>452</v>
+      </c>
+      <c r="J90" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>309</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="C91" t="s">
+        <v>311</v>
+      </c>
+      <c r="D91">
+        <v>5000</v>
+      </c>
+      <c r="E91">
+        <v>10000</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="H91" t="s">
+        <v>312</v>
+      </c>
+      <c r="I91" t="s">
+        <v>453</v>
+      </c>
+      <c r="J91" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>309</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="C92" t="s">
+        <v>311</v>
+      </c>
+      <c r="D92">
+        <v>5000</v>
+      </c>
+      <c r="E92">
+        <v>10000</v>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="H92" t="s">
+        <v>312</v>
+      </c>
+      <c r="I92" t="s">
+        <v>454</v>
+      </c>
+      <c r="J92" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>309</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="C93" t="s">
+        <v>311</v>
+      </c>
+      <c r="D93">
+        <v>5000</v>
+      </c>
+      <c r="E93">
+        <v>10000</v>
+      </c>
+      <c r="F93">
+        <v>1</v>
+      </c>
+      <c r="H93" t="s">
+        <v>312</v>
+      </c>
+      <c r="I93" t="s">
+        <v>455</v>
+      </c>
+      <c r="J93" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>309</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="C94" t="s">
+        <v>311</v>
+      </c>
+      <c r="D94">
+        <v>5000</v>
+      </c>
+      <c r="E94">
+        <v>10000</v>
+      </c>
+      <c r="F94">
+        <v>1</v>
+      </c>
+      <c r="H94" t="s">
+        <v>312</v>
+      </c>
+      <c r="I94" t="s">
+        <v>456</v>
+      </c>
+      <c r="J94" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>309</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="C95" t="s">
+        <v>311</v>
+      </c>
+      <c r="D95">
+        <v>5000</v>
+      </c>
+      <c r="E95">
+        <v>10000</v>
+      </c>
+      <c r="F95">
+        <v>1</v>
+      </c>
+      <c r="H95" t="s">
+        <v>312</v>
+      </c>
+      <c r="I95" t="s">
+        <v>457</v>
+      </c>
+      <c r="J95" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>309</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C96" t="s">
+        <v>311</v>
+      </c>
+      <c r="D96">
+        <v>5000</v>
+      </c>
+      <c r="E96">
+        <v>10000</v>
+      </c>
+      <c r="F96">
+        <v>1</v>
+      </c>
+      <c r="H96" t="s">
+        <v>312</v>
+      </c>
+      <c r="I96" t="s">
+        <v>458</v>
+      </c>
+      <c r="J96" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>309</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="C97" t="s">
+        <v>311</v>
+      </c>
+      <c r="D97">
+        <v>5000</v>
+      </c>
+      <c r="E97">
+        <v>10000</v>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+      <c r="H97" t="s">
+        <v>312</v>
+      </c>
+      <c r="I97" t="s">
+        <v>459</v>
+      </c>
+      <c r="J97" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>309</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="C98" t="s">
+        <v>311</v>
+      </c>
+      <c r="D98">
+        <v>5000</v>
+      </c>
+      <c r="E98">
+        <v>10000</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="H98" t="s">
+        <v>312</v>
+      </c>
+      <c r="I98" t="s">
+        <v>460</v>
+      </c>
+      <c r="J98" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>309</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="C99" t="s">
+        <v>311</v>
+      </c>
+      <c r="D99">
+        <v>5000</v>
+      </c>
+      <c r="E99">
+        <v>10000</v>
+      </c>
+      <c r="F99">
+        <v>1</v>
+      </c>
+      <c r="H99" t="s">
+        <v>312</v>
+      </c>
+      <c r="I99" t="s">
+        <v>461</v>
+      </c>
+      <c r="J99" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>309</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="C100" t="s">
+        <v>311</v>
+      </c>
+      <c r="D100">
+        <v>5000</v>
+      </c>
+      <c r="E100">
+        <v>10000</v>
+      </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
+      <c r="H100" t="s">
+        <v>312</v>
+      </c>
+      <c r="I100" t="s">
+        <v>462</v>
+      </c>
+      <c r="J100" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>309</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="C101" t="s">
+        <v>311</v>
+      </c>
+      <c r="D101">
+        <v>5000</v>
+      </c>
+      <c r="E101">
+        <v>10000</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="H101" t="s">
+        <v>312</v>
+      </c>
+      <c r="I101" t="s">
+        <v>463</v>
+      </c>
+      <c r="J101" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>309</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="C102" t="s">
+        <v>311</v>
+      </c>
+      <c r="D102">
+        <v>5000</v>
+      </c>
+      <c r="E102">
+        <v>10000</v>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="H102" t="s">
+        <v>312</v>
+      </c>
+      <c r="I102" t="s">
+        <v>464</v>
+      </c>
+      <c r="J102" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>309</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="C103" t="s">
+        <v>311</v>
+      </c>
+      <c r="D103">
+        <v>5000</v>
+      </c>
+      <c r="E103">
+        <v>10000</v>
+      </c>
+      <c r="F103">
+        <v>1</v>
+      </c>
+      <c r="H103" t="s">
+        <v>312</v>
+      </c>
+      <c r="I103" t="s">
+        <v>465</v>
+      </c>
+      <c r="J103" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>309</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="C104" t="s">
+        <v>311</v>
+      </c>
+      <c r="D104">
+        <v>5000</v>
+      </c>
+      <c r="E104">
+        <v>10000</v>
+      </c>
+      <c r="F104">
+        <v>1</v>
+      </c>
+      <c r="H104" t="s">
+        <v>312</v>
+      </c>
+      <c r="I104" t="s">
+        <v>466</v>
+      </c>
+      <c r="J104" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>309</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="C105" t="s">
+        <v>311</v>
+      </c>
+      <c r="D105">
+        <v>5000</v>
+      </c>
+      <c r="E105">
+        <v>10000</v>
+      </c>
+      <c r="F105">
+        <v>1</v>
+      </c>
+      <c r="H105" t="s">
+        <v>312</v>
+      </c>
+      <c r="I105" t="s">
+        <v>467</v>
+      </c>
+      <c r="J105" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>309</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="C106" t="s">
+        <v>311</v>
+      </c>
+      <c r="D106">
+        <v>5000</v>
+      </c>
+      <c r="E106">
+        <v>10000</v>
+      </c>
+      <c r="F106">
+        <v>1</v>
+      </c>
+      <c r="H106" t="s">
+        <v>312</v>
+      </c>
+      <c r="I106" t="s">
+        <v>468</v>
+      </c>
+      <c r="J106" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>309</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="C107" t="s">
+        <v>311</v>
+      </c>
+      <c r="D107">
+        <v>5000</v>
+      </c>
+      <c r="E107">
+        <v>10000</v>
+      </c>
+      <c r="F107">
+        <v>1</v>
+      </c>
+      <c r="H107" t="s">
+        <v>312</v>
+      </c>
+      <c r="I107" t="s">
+        <v>469</v>
+      </c>
+      <c r="J107" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>309</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="C108" t="s">
+        <v>311</v>
+      </c>
+      <c r="D108">
+        <v>5000</v>
+      </c>
+      <c r="E108">
+        <v>10000</v>
+      </c>
+      <c r="F108">
+        <v>1</v>
+      </c>
+      <c r="H108" t="s">
+        <v>312</v>
+      </c>
+      <c r="I108" t="s">
+        <v>470</v>
+      </c>
+      <c r="J108" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>309</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="C109" t="s">
+        <v>311</v>
+      </c>
+      <c r="D109">
+        <v>5000</v>
+      </c>
+      <c r="E109">
+        <v>10000</v>
+      </c>
+      <c r="F109">
+        <v>1</v>
+      </c>
+      <c r="H109" t="s">
+        <v>312</v>
+      </c>
+      <c r="I109" t="s">
+        <v>471</v>
+      </c>
+      <c r="J109" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>309</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="C110" t="s">
+        <v>311</v>
+      </c>
+      <c r="D110">
+        <v>5000</v>
+      </c>
+      <c r="E110">
+        <v>10000</v>
+      </c>
+      <c r="F110">
+        <v>1</v>
+      </c>
+      <c r="H110" t="s">
+        <v>312</v>
+      </c>
+      <c r="I110" t="s">
+        <v>472</v>
+      </c>
+      <c r="J110" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>309</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="C111" t="s">
+        <v>311</v>
+      </c>
+      <c r="D111">
+        <v>5000</v>
+      </c>
+      <c r="E111">
+        <v>10000</v>
+      </c>
+      <c r="F111">
+        <v>1</v>
+      </c>
+      <c r="H111" t="s">
+        <v>312</v>
+      </c>
+      <c r="I111" t="s">
+        <v>473</v>
+      </c>
+      <c r="J111" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>309</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="C112" t="s">
+        <v>311</v>
+      </c>
+      <c r="D112">
+        <v>5000</v>
+      </c>
+      <c r="E112">
+        <v>10000</v>
+      </c>
+      <c r="F112">
+        <v>1</v>
+      </c>
+      <c r="H112" t="s">
+        <v>312</v>
+      </c>
+      <c r="I112" t="s">
+        <v>474</v>
+      </c>
+      <c r="J112" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>309</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="C113" t="s">
+        <v>311</v>
+      </c>
+      <c r="D113">
+        <v>5000</v>
+      </c>
+      <c r="E113">
+        <v>10000</v>
+      </c>
+      <c r="F113">
+        <v>1</v>
+      </c>
+      <c r="H113" t="s">
+        <v>312</v>
+      </c>
+      <c r="I113" t="s">
+        <v>475</v>
+      </c>
+      <c r="J113" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>309</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="C114" t="s">
+        <v>311</v>
+      </c>
+      <c r="D114">
+        <v>5000</v>
+      </c>
+      <c r="E114">
+        <v>10000</v>
+      </c>
+      <c r="F114">
+        <v>1</v>
+      </c>
+      <c r="H114" t="s">
+        <v>312</v>
+      </c>
+      <c r="I114" t="s">
+        <v>476</v>
+      </c>
+      <c r="J114" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>309</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="C115" t="s">
+        <v>311</v>
+      </c>
+      <c r="D115">
+        <v>5000</v>
+      </c>
+      <c r="E115">
+        <v>10000</v>
+      </c>
+      <c r="F115">
+        <v>1</v>
+      </c>
+      <c r="H115" t="s">
+        <v>312</v>
+      </c>
+      <c r="I115" t="s">
+        <v>477</v>
+      </c>
+      <c r="J115" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>309</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="C116" t="s">
+        <v>311</v>
+      </c>
+      <c r="D116">
+        <v>5000</v>
+      </c>
+      <c r="E116">
+        <v>10000</v>
+      </c>
+      <c r="F116">
+        <v>1</v>
+      </c>
+      <c r="H116" t="s">
+        <v>312</v>
+      </c>
+      <c r="I116" t="s">
+        <v>478</v>
+      </c>
+      <c r="J116" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>309</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="C117" t="s">
+        <v>311</v>
+      </c>
+      <c r="D117">
+        <v>5000</v>
+      </c>
+      <c r="E117">
+        <v>10000</v>
+      </c>
+      <c r="F117">
+        <v>1</v>
+      </c>
+      <c r="H117" t="s">
+        <v>312</v>
+      </c>
+      <c r="I117" t="s">
+        <v>479</v>
+      </c>
+      <c r="J117" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>309</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="C118" t="s">
+        <v>311</v>
+      </c>
+      <c r="D118">
+        <v>5000</v>
+      </c>
+      <c r="E118">
+        <v>10000</v>
+      </c>
+      <c r="F118">
+        <v>1</v>
+      </c>
+      <c r="H118" t="s">
+        <v>312</v>
+      </c>
+      <c r="I118" t="s">
+        <v>480</v>
+      </c>
+      <c r="J118" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>309</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="C119" t="s">
+        <v>311</v>
+      </c>
+      <c r="D119">
+        <v>5000</v>
+      </c>
+      <c r="E119">
+        <v>10000</v>
+      </c>
+      <c r="F119">
+        <v>1</v>
+      </c>
+      <c r="H119" t="s">
+        <v>312</v>
+      </c>
+      <c r="I119" t="s">
+        <v>481</v>
+      </c>
+      <c r="J119" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>309</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="C120" t="s">
+        <v>311</v>
+      </c>
+      <c r="D120">
+        <v>5000</v>
+      </c>
+      <c r="E120">
+        <v>10000</v>
+      </c>
+      <c r="F120">
+        <v>1</v>
+      </c>
+      <c r="H120" t="s">
+        <v>312</v>
+      </c>
+      <c r="I120" t="s">
+        <v>482</v>
+      </c>
+      <c r="J120" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>309</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="C121" t="s">
+        <v>311</v>
+      </c>
+      <c r="D121">
+        <v>5000</v>
+      </c>
+      <c r="E121">
+        <v>10000</v>
+      </c>
+      <c r="F121">
+        <v>1</v>
+      </c>
+      <c r="H121" t="s">
+        <v>312</v>
+      </c>
+      <c r="I121" t="s">
+        <v>483</v>
+      </c>
+      <c r="J121" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>309</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="C122" t="s">
+        <v>311</v>
+      </c>
+      <c r="D122">
+        <v>5000</v>
+      </c>
+      <c r="E122">
+        <v>10000</v>
+      </c>
+      <c r="F122">
+        <v>1</v>
+      </c>
+      <c r="H122" t="s">
+        <v>312</v>
+      </c>
+      <c r="I122" t="s">
+        <v>484</v>
+      </c>
+      <c r="J122" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>309</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="C123" t="s">
+        <v>311</v>
+      </c>
+      <c r="D123">
+        <v>5000</v>
+      </c>
+      <c r="E123">
+        <v>10000</v>
+      </c>
+      <c r="F123">
+        <v>1</v>
+      </c>
+      <c r="H123" t="s">
+        <v>312</v>
+      </c>
+      <c r="I123" t="s">
+        <v>485</v>
+      </c>
+      <c r="J123" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>309</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="C124" t="s">
+        <v>311</v>
+      </c>
+      <c r="D124">
+        <v>5000</v>
+      </c>
+      <c r="E124">
+        <v>10000</v>
+      </c>
+      <c r="F124">
+        <v>1</v>
+      </c>
+      <c r="H124" t="s">
+        <v>312</v>
+      </c>
+      <c r="I124" t="s">
+        <v>486</v>
+      </c>
+      <c r="J124" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>309</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C125" t="s">
+        <v>311</v>
+      </c>
+      <c r="D125">
+        <v>5000</v>
+      </c>
+      <c r="E125">
+        <v>10000</v>
+      </c>
+      <c r="F125">
+        <v>1</v>
+      </c>
+      <c r="H125" t="s">
+        <v>312</v>
+      </c>
+      <c r="I125" t="s">
+        <v>487</v>
+      </c>
+      <c r="J125" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>309</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="C126" t="s">
+        <v>311</v>
+      </c>
+      <c r="D126">
+        <v>5000</v>
+      </c>
+      <c r="E126">
+        <v>10000</v>
+      </c>
+      <c r="F126">
+        <v>1</v>
+      </c>
+      <c r="H126" t="s">
+        <v>312</v>
+      </c>
+      <c r="I126" t="s">
+        <v>488</v>
+      </c>
+      <c r="J126" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>309</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="C127" t="s">
+        <v>311</v>
+      </c>
+      <c r="D127">
+        <v>5000</v>
+      </c>
+      <c r="E127">
+        <v>10000</v>
+      </c>
+      <c r="F127">
+        <v>1</v>
+      </c>
+      <c r="H127" t="s">
+        <v>312</v>
+      </c>
+      <c r="I127" t="s">
+        <v>489</v>
+      </c>
+      <c r="J127" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>309</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="C128" t="s">
+        <v>311</v>
+      </c>
+      <c r="D128">
+        <v>5000</v>
+      </c>
+      <c r="E128">
+        <v>10000</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+      <c r="H128" t="s">
+        <v>312</v>
+      </c>
+      <c r="I128" t="s">
+        <v>490</v>
+      </c>
+      <c r="J128" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>309</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="C129" t="s">
+        <v>311</v>
+      </c>
+      <c r="D129">
+        <v>5000</v>
+      </c>
+      <c r="E129">
+        <v>10000</v>
+      </c>
+      <c r="F129">
+        <v>1</v>
+      </c>
+      <c r="H129" t="s">
+        <v>312</v>
+      </c>
+      <c r="I129" t="s">
+        <v>491</v>
+      </c>
+      <c r="J129" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>309</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="C130" t="s">
+        <v>311</v>
+      </c>
+      <c r="D130">
+        <v>5000</v>
+      </c>
+      <c r="E130">
+        <v>10000</v>
+      </c>
+      <c r="F130">
+        <v>1</v>
+      </c>
+      <c r="H130" t="s">
+        <v>312</v>
+      </c>
+      <c r="I130" t="s">
+        <v>492</v>
+      </c>
+      <c r="J130" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>309</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="C131" t="s">
+        <v>311</v>
+      </c>
+      <c r="D131">
+        <v>5000</v>
+      </c>
+      <c r="E131">
+        <v>10000</v>
+      </c>
+      <c r="F131">
+        <v>1</v>
+      </c>
+      <c r="H131" t="s">
+        <v>312</v>
+      </c>
+      <c r="I131" t="s">
+        <v>493</v>
+      </c>
+      <c r="J131" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>309</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="C132" t="s">
+        <v>311</v>
+      </c>
+      <c r="D132">
+        <v>5000</v>
+      </c>
+      <c r="E132">
+        <v>10000</v>
+      </c>
+      <c r="F132">
+        <v>1</v>
+      </c>
+      <c r="H132" t="s">
+        <v>312</v>
+      </c>
+      <c r="I132" t="s">
+        <v>494</v>
+      </c>
+      <c r="J132" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>309</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="C133" t="s">
+        <v>311</v>
+      </c>
+      <c r="D133">
+        <v>5000</v>
+      </c>
+      <c r="E133">
+        <v>10000</v>
+      </c>
+      <c r="F133">
+        <v>1</v>
+      </c>
+      <c r="H133" t="s">
+        <v>312</v>
+      </c>
+      <c r="I133" t="s">
+        <v>495</v>
+      </c>
+      <c r="J133" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>309</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="C134" t="s">
+        <v>311</v>
+      </c>
+      <c r="D134">
+        <v>5000</v>
+      </c>
+      <c r="E134">
+        <v>10000</v>
+      </c>
+      <c r="F134">
+        <v>1</v>
+      </c>
+      <c r="H134" t="s">
+        <v>312</v>
+      </c>
+      <c r="I134" t="s">
+        <v>496</v>
+      </c>
+      <c r="J134" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>309</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="C135" t="s">
+        <v>311</v>
+      </c>
+      <c r="D135">
+        <v>5000</v>
+      </c>
+      <c r="E135">
+        <v>10000</v>
+      </c>
+      <c r="F135">
+        <v>1</v>
+      </c>
+      <c r="H135" t="s">
+        <v>312</v>
+      </c>
+      <c r="I135" t="s">
+        <v>497</v>
+      </c>
+      <c r="J135" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>309</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="C136" t="s">
+        <v>311</v>
+      </c>
+      <c r="D136">
+        <v>5000</v>
+      </c>
+      <c r="E136">
+        <v>10000</v>
+      </c>
+      <c r="F136">
+        <v>1</v>
+      </c>
+      <c r="H136" t="s">
+        <v>312</v>
+      </c>
+      <c r="I136" t="s">
+        <v>498</v>
+      </c>
+      <c r="J136" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>309</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="C137" t="s">
+        <v>311</v>
+      </c>
+      <c r="D137">
+        <v>5000</v>
+      </c>
+      <c r="E137">
+        <v>10000</v>
+      </c>
+      <c r="F137">
+        <v>1</v>
+      </c>
+      <c r="H137" t="s">
+        <v>312</v>
+      </c>
+      <c r="I137" t="s">
+        <v>499</v>
+      </c>
+      <c r="J137" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>309</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="C138" t="s">
+        <v>311</v>
+      </c>
+      <c r="D138">
+        <v>5000</v>
+      </c>
+      <c r="E138">
+        <v>10000</v>
+      </c>
+      <c r="F138">
+        <v>1</v>
+      </c>
+      <c r="H138" t="s">
+        <v>312</v>
+      </c>
+      <c r="I138" t="s">
+        <v>500</v>
+      </c>
+      <c r="J138" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>309</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="C139" t="s">
+        <v>311</v>
+      </c>
+      <c r="D139">
+        <v>5000</v>
+      </c>
+      <c r="E139">
+        <v>10000</v>
+      </c>
+      <c r="F139">
+        <v>1</v>
+      </c>
+      <c r="H139" t="s">
+        <v>312</v>
+      </c>
+      <c r="I139" t="s">
+        <v>501</v>
+      </c>
+      <c r="J139" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>309</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="C140" t="s">
+        <v>311</v>
+      </c>
+      <c r="D140">
+        <v>5000</v>
+      </c>
+      <c r="E140">
+        <v>10000</v>
+      </c>
+      <c r="F140">
+        <v>1</v>
+      </c>
+      <c r="H140" t="s">
+        <v>312</v>
+      </c>
+      <c r="I140" t="s">
+        <v>502</v>
+      </c>
+      <c r="J140" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>309</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="C141" t="s">
+        <v>311</v>
+      </c>
+      <c r="D141">
+        <v>5000</v>
+      </c>
+      <c r="E141">
+        <v>10000</v>
+      </c>
+      <c r="F141">
+        <v>1</v>
+      </c>
+      <c r="H141" t="s">
+        <v>312</v>
+      </c>
+      <c r="I141" t="s">
+        <v>503</v>
+      </c>
+      <c r="J141" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>309</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="C142" t="s">
+        <v>311</v>
+      </c>
+      <c r="D142">
+        <v>5000</v>
+      </c>
+      <c r="E142">
+        <v>10000</v>
+      </c>
+      <c r="F142">
+        <v>1</v>
+      </c>
+      <c r="H142" t="s">
+        <v>312</v>
+      </c>
+      <c r="I142" t="s">
+        <v>504</v>
+      </c>
+      <c r="J142" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>309</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="C143" t="s">
+        <v>311</v>
+      </c>
+      <c r="D143">
+        <v>5000</v>
+      </c>
+      <c r="E143">
+        <v>10000</v>
+      </c>
+      <c r="F143">
+        <v>1</v>
+      </c>
+      <c r="H143" t="s">
+        <v>312</v>
+      </c>
+      <c r="I143" t="s">
+        <v>505</v>
+      </c>
+      <c r="J143" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>309</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="C144" t="s">
+        <v>311</v>
+      </c>
+      <c r="D144">
+        <v>5000</v>
+      </c>
+      <c r="E144">
+        <v>10000</v>
+      </c>
+      <c r="F144">
+        <v>1</v>
+      </c>
+      <c r="H144" t="s">
+        <v>312</v>
+      </c>
+      <c r="I144" t="s">
+        <v>506</v>
+      </c>
+      <c r="J144" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>309</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="C145" t="s">
+        <v>311</v>
+      </c>
+      <c r="D145">
+        <v>5000</v>
+      </c>
+      <c r="E145">
+        <v>10000</v>
+      </c>
+      <c r="F145">
+        <v>1</v>
+      </c>
+      <c r="H145" t="s">
+        <v>312</v>
+      </c>
+      <c r="I145" t="s">
+        <v>507</v>
+      </c>
+      <c r="J145" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>309</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="C146" t="s">
+        <v>311</v>
+      </c>
+      <c r="D146">
+        <v>5000</v>
+      </c>
+      <c r="E146">
+        <v>10000</v>
+      </c>
+      <c r="F146">
+        <v>1</v>
+      </c>
+      <c r="H146" t="s">
+        <v>312</v>
+      </c>
+      <c r="I146" t="s">
+        <v>508</v>
+      </c>
+      <c r="J146" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>309</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="C147" t="s">
+        <v>311</v>
+      </c>
+      <c r="D147">
+        <v>5000</v>
+      </c>
+      <c r="E147">
+        <v>10000</v>
+      </c>
+      <c r="F147">
+        <v>1</v>
+      </c>
+      <c r="H147" t="s">
+        <v>312</v>
+      </c>
+      <c r="I147" t="s">
+        <v>509</v>
+      </c>
+      <c r="J147" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>309</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="C148" t="s">
+        <v>311</v>
+      </c>
+      <c r="D148">
+        <v>5000</v>
+      </c>
+      <c r="E148">
+        <v>10000</v>
+      </c>
+      <c r="F148">
+        <v>1</v>
+      </c>
+      <c r="H148" t="s">
+        <v>312</v>
+      </c>
+      <c r="I148" t="s">
+        <v>510</v>
+      </c>
+      <c r="J148" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>309</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="C149" t="s">
+        <v>311</v>
+      </c>
+      <c r="D149">
+        <v>5000</v>
+      </c>
+      <c r="E149">
+        <v>10000</v>
+      </c>
+      <c r="F149">
+        <v>1</v>
+      </c>
+      <c r="H149" t="s">
+        <v>312</v>
+      </c>
+      <c r="I149" t="s">
+        <v>511</v>
+      </c>
+      <c r="J149" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>309</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="C150" t="s">
+        <v>311</v>
+      </c>
+      <c r="D150">
+        <v>5000</v>
+      </c>
+      <c r="E150">
+        <v>10000</v>
+      </c>
+      <c r="F150">
+        <v>1</v>
+      </c>
+      <c r="H150" t="s">
+        <v>312</v>
+      </c>
+      <c r="I150" t="s">
+        <v>512</v>
+      </c>
+      <c r="J150" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>309</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="C151" t="s">
+        <v>311</v>
+      </c>
+      <c r="D151">
+        <v>5000</v>
+      </c>
+      <c r="E151">
+        <v>10000</v>
+      </c>
+      <c r="F151">
+        <v>1</v>
+      </c>
+      <c r="H151" t="s">
+        <v>312</v>
+      </c>
+      <c r="I151" t="s">
+        <v>513</v>
+      </c>
+      <c r="J151" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>309</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="C152" t="s">
+        <v>311</v>
+      </c>
+      <c r="D152">
+        <v>5000</v>
+      </c>
+      <c r="E152">
+        <v>10000</v>
+      </c>
+      <c r="F152">
+        <v>1</v>
+      </c>
+      <c r="H152" t="s">
+        <v>312</v>
+      </c>
+      <c r="I152" t="s">
+        <v>514</v>
+      </c>
+      <c r="J152" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>309</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="C153" t="s">
+        <v>311</v>
+      </c>
+      <c r="D153">
+        <v>5000</v>
+      </c>
+      <c r="E153">
+        <v>10000</v>
+      </c>
+      <c r="F153">
+        <v>1</v>
+      </c>
+      <c r="H153" t="s">
+        <v>312</v>
+      </c>
+      <c r="I153" t="s">
+        <v>515</v>
+      </c>
+      <c r="J153" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>309</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="C154" t="s">
+        <v>311</v>
+      </c>
+      <c r="D154">
+        <v>5000</v>
+      </c>
+      <c r="E154">
+        <v>10000</v>
+      </c>
+      <c r="F154">
+        <v>1</v>
+      </c>
+      <c r="H154" t="s">
+        <v>312</v>
+      </c>
+      <c r="I154" t="s">
+        <v>516</v>
+      </c>
+      <c r="J154" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>309</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="C155" t="s">
+        <v>311</v>
+      </c>
+      <c r="D155">
+        <v>5000</v>
+      </c>
+      <c r="E155">
+        <v>10000</v>
+      </c>
+      <c r="F155">
+        <v>1</v>
+      </c>
+      <c r="H155" t="s">
+        <v>312</v>
+      </c>
+      <c r="I155" t="s">
+        <v>517</v>
+      </c>
+      <c r="J155" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>309</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="C156" t="s">
+        <v>311</v>
+      </c>
+      <c r="D156">
+        <v>5000</v>
+      </c>
+      <c r="E156">
+        <v>10000</v>
+      </c>
+      <c r="F156">
+        <v>1</v>
+      </c>
+      <c r="H156" t="s">
+        <v>312</v>
+      </c>
+      <c r="I156" t="s">
+        <v>518</v>
+      </c>
+      <c r="J156" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>309</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="C157" t="s">
+        <v>311</v>
+      </c>
+      <c r="D157">
+        <v>5000</v>
+      </c>
+      <c r="E157">
+        <v>10000</v>
+      </c>
+      <c r="F157">
+        <v>1</v>
+      </c>
+      <c r="H157" t="s">
+        <v>312</v>
+      </c>
+      <c r="I157" t="s">
+        <v>519</v>
+      </c>
+      <c r="J157" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>309</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="C158" t="s">
+        <v>311</v>
+      </c>
+      <c r="D158">
+        <v>5000</v>
+      </c>
+      <c r="E158">
+        <v>10000</v>
+      </c>
+      <c r="F158">
+        <v>1</v>
+      </c>
+      <c r="H158" t="s">
+        <v>312</v>
+      </c>
+      <c r="I158" t="s">
+        <v>520</v>
+      </c>
+      <c r="J158" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>309</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C159" t="s">
+        <v>311</v>
+      </c>
+      <c r="D159">
+        <v>5000</v>
+      </c>
+      <c r="E159">
+        <v>10000</v>
+      </c>
+      <c r="F159">
+        <v>1</v>
+      </c>
+      <c r="H159" t="s">
+        <v>312</v>
+      </c>
+      <c r="I159" t="s">
+        <v>521</v>
+      </c>
+      <c r="J159" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>309</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="C160" t="s">
+        <v>311</v>
+      </c>
+      <c r="D160">
+        <v>5000</v>
+      </c>
+      <c r="E160">
+        <v>10000</v>
+      </c>
+      <c r="F160">
+        <v>1</v>
+      </c>
+      <c r="H160" t="s">
+        <v>312</v>
+      </c>
+      <c r="I160" t="s">
+        <v>522</v>
+      </c>
+      <c r="J160" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>309</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="C161" t="s">
+        <v>311</v>
+      </c>
+      <c r="D161">
+        <v>5000</v>
+      </c>
+      <c r="E161">
+        <v>10000</v>
+      </c>
+      <c r="F161">
+        <v>1</v>
+      </c>
+      <c r="H161" t="s">
+        <v>312</v>
+      </c>
+      <c r="I161" t="s">
+        <v>523</v>
+      </c>
+      <c r="J161" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>309</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="C162" t="s">
+        <v>311</v>
+      </c>
+      <c r="D162">
+        <v>5000</v>
+      </c>
+      <c r="E162">
+        <v>10000</v>
+      </c>
+      <c r="F162">
+        <v>1</v>
+      </c>
+      <c r="H162" t="s">
+        <v>312</v>
+      </c>
+      <c r="I162" t="s">
+        <v>524</v>
+      </c>
+      <c r="J162" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>309</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="C163" t="s">
+        <v>311</v>
+      </c>
+      <c r="D163">
+        <v>5000</v>
+      </c>
+      <c r="E163">
+        <v>10000</v>
+      </c>
+      <c r="F163">
+        <v>1</v>
+      </c>
+      <c r="H163" t="s">
+        <v>312</v>
+      </c>
+      <c r="I163" t="s">
+        <v>525</v>
+      </c>
+      <c r="J163" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>309</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="C164" t="s">
+        <v>311</v>
+      </c>
+      <c r="D164">
+        <v>5000</v>
+      </c>
+      <c r="E164">
+        <v>10000</v>
+      </c>
+      <c r="F164">
+        <v>1</v>
+      </c>
+      <c r="H164" t="s">
+        <v>312</v>
+      </c>
+      <c r="I164" t="s">
+        <v>526</v>
+      </c>
+      <c r="J164" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>309</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C165" t="s">
+        <v>311</v>
+      </c>
+      <c r="D165">
+        <v>5000</v>
+      </c>
+      <c r="E165">
+        <v>10000</v>
+      </c>
+      <c r="F165">
+        <v>1</v>
+      </c>
+      <c r="H165" t="s">
+        <v>312</v>
+      </c>
+      <c r="I165" t="s">
+        <v>527</v>
+      </c>
+      <c r="J165" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
+        <v>309</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="C166" t="s">
+        <v>311</v>
+      </c>
+      <c r="D166">
+        <v>5000</v>
+      </c>
+      <c r="E166">
+        <v>10000</v>
+      </c>
+      <c r="F166">
+        <v>1</v>
+      </c>
+      <c r="H166" t="s">
+        <v>312</v>
+      </c>
+      <c r="I166" t="s">
+        <v>528</v>
+      </c>
+      <c r="J166" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>309</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="C167" t="s">
+        <v>311</v>
+      </c>
+      <c r="D167">
+        <v>5000</v>
+      </c>
+      <c r="E167">
+        <v>10000</v>
+      </c>
+      <c r="F167">
+        <v>1</v>
+      </c>
+      <c r="H167" t="s">
+        <v>312</v>
+      </c>
+      <c r="I167" t="s">
+        <v>529</v>
+      </c>
+      <c r="J167" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>309</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="C168" t="s">
+        <v>311</v>
+      </c>
+      <c r="D168">
+        <v>5000</v>
+      </c>
+      <c r="E168">
+        <v>10000</v>
+      </c>
+      <c r="F168">
+        <v>1</v>
+      </c>
+      <c r="H168" t="s">
+        <v>312</v>
+      </c>
+      <c r="I168" t="s">
+        <v>530</v>
+      </c>
+      <c r="J168" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>309</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="C169" t="s">
+        <v>311</v>
+      </c>
+      <c r="D169">
+        <v>5000</v>
+      </c>
+      <c r="E169">
+        <v>10000</v>
+      </c>
+      <c r="F169">
+        <v>1</v>
+      </c>
+      <c r="H169" t="s">
+        <v>312</v>
+      </c>
+      <c r="I169" t="s">
+        <v>531</v>
+      </c>
+      <c r="J169" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>309</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="C170" t="s">
+        <v>311</v>
+      </c>
+      <c r="D170">
+        <v>5000</v>
+      </c>
+      <c r="E170">
+        <v>10000</v>
+      </c>
+      <c r="F170">
+        <v>1</v>
+      </c>
+      <c r="H170" t="s">
+        <v>312</v>
+      </c>
+      <c r="I170" t="s">
+        <v>532</v>
+      </c>
+      <c r="J170" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>309</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="C171" t="s">
+        <v>311</v>
+      </c>
+      <c r="D171">
+        <v>5000</v>
+      </c>
+      <c r="E171">
+        <v>10000</v>
+      </c>
+      <c r="F171">
+        <v>1</v>
+      </c>
+      <c r="H171" t="s">
+        <v>312</v>
+      </c>
+      <c r="I171" t="s">
+        <v>533</v>
+      </c>
+      <c r="J171" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>309</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="C172" t="s">
+        <v>311</v>
+      </c>
+      <c r="D172">
+        <v>5000</v>
+      </c>
+      <c r="E172">
+        <v>10000</v>
+      </c>
+      <c r="F172">
+        <v>1</v>
+      </c>
+      <c r="H172" t="s">
+        <v>312</v>
+      </c>
+      <c r="I172" t="s">
+        <v>534</v>
+      </c>
+      <c r="J172" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>309</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="C173" t="s">
+        <v>311</v>
+      </c>
+      <c r="D173">
+        <v>5000</v>
+      </c>
+      <c r="E173">
+        <v>10000</v>
+      </c>
+      <c r="F173">
+        <v>1</v>
+      </c>
+      <c r="H173" t="s">
+        <v>312</v>
+      </c>
+      <c r="I173" t="s">
+        <v>535</v>
+      </c>
+      <c r="J173" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>309</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="C174" t="s">
+        <v>311</v>
+      </c>
+      <c r="D174">
+        <v>5000</v>
+      </c>
+      <c r="E174">
+        <v>10000</v>
+      </c>
+      <c r="F174">
+        <v>1</v>
+      </c>
+      <c r="H174" t="s">
+        <v>312</v>
+      </c>
+      <c r="I174" t="s">
+        <v>536</v>
+      </c>
+      <c r="J174" t="s">
+        <v>313</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0276408-E7B3-4582-AFCE-9FBABB6C4FB2}">
+  <dimension ref="A1:F113"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="26.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1" t="s">
+        <v>537</v>
+      </c>
+      <c r="D1">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>538</v>
+      </c>
+      <c r="F1" t="str">
+        <f>_xlfn.CONCAT(C1,D1,E1)</f>
+        <v>img/coleccionables/ca1.jpg</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C2" t="s">
+        <v>537</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>538</v>
+      </c>
+      <c r="F2" t="str">
+        <f t="shared" ref="F2:F65" si="0">_xlfn.CONCAT(C2,D2,E2)</f>
+        <v>img/coleccionables/ca2.jpg</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C3" t="s">
+        <v>537</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>538</v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca3.jpg</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C4" t="s">
+        <v>537</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>538</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca4.jpg</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C5" t="s">
+        <v>537</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>538</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca5.jpg</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>318</v>
+      </c>
+      <c r="C6" t="s">
+        <v>537</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6" t="s">
+        <v>538</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca6.jpg</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>319</v>
+      </c>
+      <c r="C7" t="s">
+        <v>537</v>
+      </c>
+      <c r="D7">
+        <v>7</v>
+      </c>
+      <c r="E7" t="s">
+        <v>538</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca7.jpg</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>320</v>
+      </c>
+      <c r="C8" t="s">
+        <v>537</v>
+      </c>
+      <c r="D8">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
+        <v>538</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca8.jpg</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>321</v>
+      </c>
+      <c r="C9" t="s">
+        <v>537</v>
+      </c>
+      <c r="D9">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s">
+        <v>538</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca9.jpg</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>322</v>
+      </c>
+      <c r="C10" t="s">
+        <v>537</v>
+      </c>
+      <c r="D10">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>538</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca10.jpg</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C11" t="s">
+        <v>537</v>
+      </c>
+      <c r="D11">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>538</v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca11.jpg</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>324</v>
+      </c>
+      <c r="C12" t="s">
+        <v>537</v>
+      </c>
+      <c r="D12">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>538</v>
+      </c>
+      <c r="F12" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca12.jpg</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>325</v>
+      </c>
+      <c r="C13" t="s">
+        <v>537</v>
+      </c>
+      <c r="D13">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>538</v>
+      </c>
+      <c r="F13" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca13.jpg</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>326</v>
+      </c>
+      <c r="C14" t="s">
+        <v>537</v>
+      </c>
+      <c r="D14">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s">
+        <v>538</v>
+      </c>
+      <c r="F14" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca14.jpg</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>327</v>
+      </c>
+      <c r="C15" t="s">
+        <v>537</v>
+      </c>
+      <c r="D15">
+        <v>15</v>
+      </c>
+      <c r="E15" t="s">
+        <v>538</v>
+      </c>
+      <c r="F15" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca15.jpg</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>328</v>
+      </c>
+      <c r="C16" t="s">
+        <v>537</v>
+      </c>
+      <c r="D16">
+        <v>16</v>
+      </c>
+      <c r="E16" t="s">
+        <v>538</v>
+      </c>
+      <c r="F16" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca16.jpg</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>329</v>
+      </c>
+      <c r="C17" t="s">
+        <v>537</v>
+      </c>
+      <c r="D17">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s">
+        <v>538</v>
+      </c>
+      <c r="F17" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca17.jpg</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>330</v>
+      </c>
+      <c r="C18" t="s">
+        <v>537</v>
+      </c>
+      <c r="D18">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
+        <v>538</v>
+      </c>
+      <c r="F18" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca18.jpg</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>331</v>
+      </c>
+      <c r="C19" t="s">
+        <v>537</v>
+      </c>
+      <c r="D19">
+        <v>19</v>
+      </c>
+      <c r="E19" t="s">
+        <v>538</v>
+      </c>
+      <c r="F19" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca19.jpg</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>332</v>
+      </c>
+      <c r="C20" t="s">
+        <v>537</v>
+      </c>
+      <c r="D20">
+        <v>20</v>
+      </c>
+      <c r="E20" t="s">
+        <v>538</v>
+      </c>
+      <c r="F20" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca20.jpg</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>333</v>
+      </c>
+      <c r="C21" t="s">
+        <v>537</v>
+      </c>
+      <c r="D21">
+        <v>21</v>
+      </c>
+      <c r="E21" t="s">
+        <v>538</v>
+      </c>
+      <c r="F21" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca21.jpg</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>334</v>
+      </c>
+      <c r="C22" t="s">
+        <v>537</v>
+      </c>
+      <c r="D22">
+        <v>22</v>
+      </c>
+      <c r="E22" t="s">
+        <v>538</v>
+      </c>
+      <c r="F22" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca22.jpg</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>335</v>
+      </c>
+      <c r="C23" t="s">
+        <v>537</v>
+      </c>
+      <c r="D23">
+        <v>23</v>
+      </c>
+      <c r="E23" t="s">
+        <v>538</v>
+      </c>
+      <c r="F23" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca23.jpg</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>336</v>
+      </c>
+      <c r="C24" t="s">
+        <v>537</v>
+      </c>
+      <c r="D24">
+        <v>24</v>
+      </c>
+      <c r="E24" t="s">
+        <v>538</v>
+      </c>
+      <c r="F24" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca24.jpg</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>337</v>
+      </c>
+      <c r="C25" t="s">
+        <v>537</v>
+      </c>
+      <c r="D25">
+        <v>25</v>
+      </c>
+      <c r="E25" t="s">
+        <v>538</v>
+      </c>
+      <c r="F25" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca25.jpg</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>338</v>
+      </c>
+      <c r="C26" t="s">
+        <v>537</v>
+      </c>
+      <c r="D26">
+        <v>26</v>
+      </c>
+      <c r="E26" t="s">
+        <v>538</v>
+      </c>
+      <c r="F26" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca26.jpg</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>339</v>
+      </c>
+      <c r="C27" t="s">
+        <v>537</v>
+      </c>
+      <c r="D27">
+        <v>27</v>
+      </c>
+      <c r="E27" t="s">
+        <v>538</v>
+      </c>
+      <c r="F27" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca27.jpg</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>340</v>
+      </c>
+      <c r="C28" t="s">
+        <v>537</v>
+      </c>
+      <c r="D28">
+        <v>28</v>
+      </c>
+      <c r="E28" t="s">
+        <v>538</v>
+      </c>
+      <c r="F28" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca28.jpg</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>341</v>
+      </c>
+      <c r="C29" t="s">
+        <v>537</v>
+      </c>
+      <c r="D29">
+        <v>29</v>
+      </c>
+      <c r="E29" t="s">
+        <v>538</v>
+      </c>
+      <c r="F29" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca29.jpg</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>342</v>
+      </c>
+      <c r="C30" t="s">
+        <v>537</v>
+      </c>
+      <c r="D30">
+        <v>30</v>
+      </c>
+      <c r="E30" t="s">
+        <v>538</v>
+      </c>
+      <c r="F30" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca30.jpg</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>343</v>
+      </c>
+      <c r="C31" t="s">
+        <v>537</v>
+      </c>
+      <c r="D31">
+        <v>31</v>
+      </c>
+      <c r="E31" t="s">
+        <v>538</v>
+      </c>
+      <c r="F31" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca31.jpg</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>344</v>
+      </c>
+      <c r="C32" t="s">
+        <v>537</v>
+      </c>
+      <c r="D32">
+        <v>32</v>
+      </c>
+      <c r="E32" t="s">
+        <v>538</v>
+      </c>
+      <c r="F32" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca32.jpg</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>345</v>
+      </c>
+      <c r="C33" t="s">
+        <v>537</v>
+      </c>
+      <c r="D33">
+        <v>33</v>
+      </c>
+      <c r="E33" t="s">
+        <v>538</v>
+      </c>
+      <c r="F33" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca33.jpg</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>346</v>
+      </c>
+      <c r="C34" t="s">
+        <v>537</v>
+      </c>
+      <c r="D34">
+        <v>34</v>
+      </c>
+      <c r="E34" t="s">
+        <v>538</v>
+      </c>
+      <c r="F34" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca34.jpg</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>347</v>
+      </c>
+      <c r="C35" t="s">
+        <v>537</v>
+      </c>
+      <c r="D35">
+        <v>35</v>
+      </c>
+      <c r="E35" t="s">
+        <v>538</v>
+      </c>
+      <c r="F35" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca35.jpg</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>348</v>
+      </c>
+      <c r="C36" t="s">
+        <v>537</v>
+      </c>
+      <c r="D36">
+        <v>36</v>
+      </c>
+      <c r="E36" t="s">
+        <v>538</v>
+      </c>
+      <c r="F36" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca36.jpg</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>349</v>
+      </c>
+      <c r="C37" t="s">
+        <v>537</v>
+      </c>
+      <c r="D37">
+        <v>37</v>
+      </c>
+      <c r="E37" t="s">
+        <v>538</v>
+      </c>
+      <c r="F37" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca37.jpg</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>350</v>
+      </c>
+      <c r="C38" t="s">
+        <v>537</v>
+      </c>
+      <c r="D38">
+        <v>38</v>
+      </c>
+      <c r="E38" t="s">
+        <v>538</v>
+      </c>
+      <c r="F38" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca38.jpg</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>351</v>
+      </c>
+      <c r="C39" t="s">
+        <v>537</v>
+      </c>
+      <c r="D39">
+        <v>39</v>
+      </c>
+      <c r="E39" t="s">
+        <v>538</v>
+      </c>
+      <c r="F39" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca39.jpg</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>352</v>
+      </c>
+      <c r="C40" t="s">
+        <v>537</v>
+      </c>
+      <c r="D40">
+        <v>40</v>
+      </c>
+      <c r="E40" t="s">
+        <v>538</v>
+      </c>
+      <c r="F40" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca40.jpg</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>353</v>
+      </c>
+      <c r="C41" t="s">
+        <v>537</v>
+      </c>
+      <c r="D41">
+        <v>41</v>
+      </c>
+      <c r="E41" t="s">
+        <v>538</v>
+      </c>
+      <c r="F41" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca41.jpg</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>354</v>
+      </c>
+      <c r="C42" t="s">
+        <v>537</v>
+      </c>
+      <c r="D42">
+        <v>42</v>
+      </c>
+      <c r="E42" t="s">
+        <v>538</v>
+      </c>
+      <c r="F42" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca42.jpg</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>355</v>
+      </c>
+      <c r="C43" t="s">
+        <v>537</v>
+      </c>
+      <c r="D43">
+        <v>43</v>
+      </c>
+      <c r="E43" t="s">
+        <v>538</v>
+      </c>
+      <c r="F43" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca43.jpg</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>356</v>
+      </c>
+      <c r="C44" t="s">
+        <v>537</v>
+      </c>
+      <c r="D44">
+        <v>44</v>
+      </c>
+      <c r="E44" t="s">
+        <v>538</v>
+      </c>
+      <c r="F44" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca44.jpg</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>357</v>
+      </c>
+      <c r="C45" t="s">
+        <v>537</v>
+      </c>
+      <c r="D45">
+        <v>45</v>
+      </c>
+      <c r="E45" t="s">
+        <v>538</v>
+      </c>
+      <c r="F45" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca45.jpg</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>358</v>
+      </c>
+      <c r="C46" t="s">
+        <v>537</v>
+      </c>
+      <c r="D46">
+        <v>46</v>
+      </c>
+      <c r="E46" t="s">
+        <v>538</v>
+      </c>
+      <c r="F46" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca46.jpg</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>359</v>
+      </c>
+      <c r="C47" t="s">
+        <v>537</v>
+      </c>
+      <c r="D47">
+        <v>47</v>
+      </c>
+      <c r="E47" t="s">
+        <v>538</v>
+      </c>
+      <c r="F47" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca47.jpg</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>360</v>
+      </c>
+      <c r="C48" t="s">
+        <v>537</v>
+      </c>
+      <c r="D48">
+        <v>48</v>
+      </c>
+      <c r="E48" t="s">
+        <v>538</v>
+      </c>
+      <c r="F48" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca48.jpg</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>361</v>
+      </c>
+      <c r="C49" t="s">
+        <v>537</v>
+      </c>
+      <c r="D49">
+        <v>49</v>
+      </c>
+      <c r="E49" t="s">
+        <v>538</v>
+      </c>
+      <c r="F49" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca49.jpg</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>362</v>
+      </c>
+      <c r="C50" t="s">
+        <v>537</v>
+      </c>
+      <c r="D50">
+        <v>50</v>
+      </c>
+      <c r="E50" t="s">
+        <v>538</v>
+      </c>
+      <c r="F50" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca50.jpg</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>363</v>
+      </c>
+      <c r="C51" t="s">
+        <v>537</v>
+      </c>
+      <c r="D51">
+        <v>51</v>
+      </c>
+      <c r="E51" t="s">
+        <v>538</v>
+      </c>
+      <c r="F51" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca51.jpg</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>364</v>
+      </c>
+      <c r="C52" t="s">
+        <v>537</v>
+      </c>
+      <c r="D52">
+        <v>52</v>
+      </c>
+      <c r="E52" t="s">
+        <v>538</v>
+      </c>
+      <c r="F52" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca52.jpg</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>365</v>
+      </c>
+      <c r="C53" t="s">
+        <v>537</v>
+      </c>
+      <c r="D53">
+        <v>53</v>
+      </c>
+      <c r="E53" t="s">
+        <v>538</v>
+      </c>
+      <c r="F53" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca53.jpg</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>366</v>
+      </c>
+      <c r="C54" t="s">
+        <v>537</v>
+      </c>
+      <c r="D54">
+        <v>54</v>
+      </c>
+      <c r="E54" t="s">
+        <v>538</v>
+      </c>
+      <c r="F54" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca54.jpg</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>367</v>
+      </c>
+      <c r="C55" t="s">
+        <v>537</v>
+      </c>
+      <c r="D55">
+        <v>55</v>
+      </c>
+      <c r="E55" t="s">
+        <v>538</v>
+      </c>
+      <c r="F55" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca55.jpg</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>368</v>
+      </c>
+      <c r="C56" t="s">
+        <v>537</v>
+      </c>
+      <c r="D56">
+        <v>56</v>
+      </c>
+      <c r="E56" t="s">
+        <v>538</v>
+      </c>
+      <c r="F56" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca56.jpg</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>369</v>
+      </c>
+      <c r="C57" t="s">
+        <v>537</v>
+      </c>
+      <c r="D57">
+        <v>57</v>
+      </c>
+      <c r="E57" t="s">
+        <v>538</v>
+      </c>
+      <c r="F57" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca57.jpg</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>370</v>
+      </c>
+      <c r="C58" t="s">
+        <v>537</v>
+      </c>
+      <c r="D58">
+        <v>58</v>
+      </c>
+      <c r="E58" t="s">
+        <v>538</v>
+      </c>
+      <c r="F58" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca58.jpg</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>371</v>
+      </c>
+      <c r="C59" t="s">
+        <v>537</v>
+      </c>
+      <c r="D59">
+        <v>59</v>
+      </c>
+      <c r="E59" t="s">
+        <v>538</v>
+      </c>
+      <c r="F59" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca59.jpg</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>372</v>
+      </c>
+      <c r="C60" t="s">
+        <v>537</v>
+      </c>
+      <c r="D60">
+        <v>60</v>
+      </c>
+      <c r="E60" t="s">
+        <v>538</v>
+      </c>
+      <c r="F60" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca60.jpg</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>373</v>
+      </c>
+      <c r="C61" t="s">
+        <v>537</v>
+      </c>
+      <c r="D61">
+        <v>61</v>
+      </c>
+      <c r="E61" t="s">
+        <v>538</v>
+      </c>
+      <c r="F61" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca61.jpg</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>374</v>
+      </c>
+      <c r="C62" t="s">
+        <v>537</v>
+      </c>
+      <c r="D62">
+        <v>62</v>
+      </c>
+      <c r="E62" t="s">
+        <v>538</v>
+      </c>
+      <c r="F62" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca62.jpg</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>375</v>
+      </c>
+      <c r="C63" t="s">
+        <v>537</v>
+      </c>
+      <c r="D63">
+        <v>63</v>
+      </c>
+      <c r="E63" t="s">
+        <v>538</v>
+      </c>
+      <c r="F63" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca63.jpg</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>376</v>
+      </c>
+      <c r="C64" t="s">
+        <v>537</v>
+      </c>
+      <c r="D64">
+        <v>64</v>
+      </c>
+      <c r="E64" t="s">
+        <v>538</v>
+      </c>
+      <c r="F64" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca64.jpg</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>377</v>
+      </c>
+      <c r="C65" t="s">
+        <v>537</v>
+      </c>
+      <c r="D65">
+        <v>65</v>
+      </c>
+      <c r="E65" t="s">
+        <v>538</v>
+      </c>
+      <c r="F65" t="str">
+        <f t="shared" si="0"/>
+        <v>img/coleccionables/ca65.jpg</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>378</v>
+      </c>
+      <c r="C66" t="s">
+        <v>537</v>
+      </c>
+      <c r="D66">
+        <v>66</v>
+      </c>
+      <c r="E66" t="s">
+        <v>538</v>
+      </c>
+      <c r="F66" t="str">
+        <f t="shared" ref="F66:F113" si="1">_xlfn.CONCAT(C66,D66,E66)</f>
+        <v>img/coleccionables/ca66.jpg</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>379</v>
+      </c>
+      <c r="C67" t="s">
+        <v>537</v>
+      </c>
+      <c r="D67">
+        <v>67</v>
+      </c>
+      <c r="E67" t="s">
+        <v>538</v>
+      </c>
+      <c r="F67" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca67.jpg</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>380</v>
+      </c>
+      <c r="C68" t="s">
+        <v>537</v>
+      </c>
+      <c r="D68">
+        <v>68</v>
+      </c>
+      <c r="E68" t="s">
+        <v>538</v>
+      </c>
+      <c r="F68" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca68.jpg</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>381</v>
+      </c>
+      <c r="C69" t="s">
+        <v>537</v>
+      </c>
+      <c r="D69">
+        <v>69</v>
+      </c>
+      <c r="E69" t="s">
+        <v>538</v>
+      </c>
+      <c r="F69" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca69.jpg</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>382</v>
+      </c>
+      <c r="C70" t="s">
+        <v>537</v>
+      </c>
+      <c r="D70">
+        <v>70</v>
+      </c>
+      <c r="E70" t="s">
+        <v>538</v>
+      </c>
+      <c r="F70" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca70.jpg</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>383</v>
+      </c>
+      <c r="C71" t="s">
+        <v>537</v>
+      </c>
+      <c r="D71">
+        <v>71</v>
+      </c>
+      <c r="E71" t="s">
+        <v>538</v>
+      </c>
+      <c r="F71" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca71.jpg</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>384</v>
+      </c>
+      <c r="C72" t="s">
+        <v>537</v>
+      </c>
+      <c r="D72">
+        <v>72</v>
+      </c>
+      <c r="E72" t="s">
+        <v>538</v>
+      </c>
+      <c r="F72" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca72.jpg</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>385</v>
+      </c>
+      <c r="C73" t="s">
+        <v>537</v>
+      </c>
+      <c r="D73">
+        <v>73</v>
+      </c>
+      <c r="E73" t="s">
+        <v>538</v>
+      </c>
+      <c r="F73" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca73.jpg</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>386</v>
+      </c>
+      <c r="C74" t="s">
+        <v>537</v>
+      </c>
+      <c r="D74">
+        <v>74</v>
+      </c>
+      <c r="E74" t="s">
+        <v>538</v>
+      </c>
+      <c r="F74" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca74.jpg</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>387</v>
+      </c>
+      <c r="C75" t="s">
+        <v>537</v>
+      </c>
+      <c r="D75">
+        <v>75</v>
+      </c>
+      <c r="E75" t="s">
+        <v>538</v>
+      </c>
+      <c r="F75" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca75.jpg</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>388</v>
+      </c>
+      <c r="C76" t="s">
+        <v>537</v>
+      </c>
+      <c r="D76">
+        <v>76</v>
+      </c>
+      <c r="E76" t="s">
+        <v>538</v>
+      </c>
+      <c r="F76" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca76.jpg</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>389</v>
+      </c>
+      <c r="C77" t="s">
+        <v>537</v>
+      </c>
+      <c r="D77">
+        <v>77</v>
+      </c>
+      <c r="E77" t="s">
+        <v>538</v>
+      </c>
+      <c r="F77" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca77.jpg</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>390</v>
+      </c>
+      <c r="C78" t="s">
+        <v>537</v>
+      </c>
+      <c r="D78">
+        <v>78</v>
+      </c>
+      <c r="E78" t="s">
+        <v>538</v>
+      </c>
+      <c r="F78" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca78.jpg</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>391</v>
+      </c>
+      <c r="C79" t="s">
+        <v>537</v>
+      </c>
+      <c r="D79">
+        <v>79</v>
+      </c>
+      <c r="E79" t="s">
+        <v>538</v>
+      </c>
+      <c r="F79" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca79.jpg</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>392</v>
+      </c>
+      <c r="C80" t="s">
+        <v>537</v>
+      </c>
+      <c r="D80">
+        <v>80</v>
+      </c>
+      <c r="E80" t="s">
+        <v>538</v>
+      </c>
+      <c r="F80" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca80.jpg</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>393</v>
+      </c>
+      <c r="C81" t="s">
+        <v>537</v>
+      </c>
+      <c r="D81">
+        <v>81</v>
+      </c>
+      <c r="E81" t="s">
+        <v>538</v>
+      </c>
+      <c r="F81" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca81.jpg</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>394</v>
+      </c>
+      <c r="C82" t="s">
+        <v>537</v>
+      </c>
+      <c r="D82">
+        <v>82</v>
+      </c>
+      <c r="E82" t="s">
+        <v>538</v>
+      </c>
+      <c r="F82" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca82.jpg</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>395</v>
+      </c>
+      <c r="C83" t="s">
+        <v>537</v>
+      </c>
+      <c r="D83">
+        <v>83</v>
+      </c>
+      <c r="E83" t="s">
+        <v>538</v>
+      </c>
+      <c r="F83" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca83.jpg</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>396</v>
+      </c>
+      <c r="C84" t="s">
+        <v>537</v>
+      </c>
+      <c r="D84">
+        <v>84</v>
+      </c>
+      <c r="E84" t="s">
+        <v>538</v>
+      </c>
+      <c r="F84" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca84.jpg</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>397</v>
+      </c>
+      <c r="C85" t="s">
+        <v>537</v>
+      </c>
+      <c r="D85">
+        <v>85</v>
+      </c>
+      <c r="E85" t="s">
+        <v>538</v>
+      </c>
+      <c r="F85" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca85.jpg</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>398</v>
+      </c>
+      <c r="C86" t="s">
+        <v>537</v>
+      </c>
+      <c r="D86">
+        <v>86</v>
+      </c>
+      <c r="E86" t="s">
+        <v>538</v>
+      </c>
+      <c r="F86" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca86.jpg</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>399</v>
+      </c>
+      <c r="C87" t="s">
+        <v>537</v>
+      </c>
+      <c r="D87">
+        <v>87</v>
+      </c>
+      <c r="E87" t="s">
+        <v>538</v>
+      </c>
+      <c r="F87" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca87.jpg</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>400</v>
+      </c>
+      <c r="C88" t="s">
+        <v>537</v>
+      </c>
+      <c r="D88">
+        <v>88</v>
+      </c>
+      <c r="E88" t="s">
+        <v>538</v>
+      </c>
+      <c r="F88" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca88.jpg</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>401</v>
+      </c>
+      <c r="C89" t="s">
+        <v>537</v>
+      </c>
+      <c r="D89">
+        <v>89</v>
+      </c>
+      <c r="E89" t="s">
+        <v>538</v>
+      </c>
+      <c r="F89" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca89.jpg</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>402</v>
+      </c>
+      <c r="C90" t="s">
+        <v>537</v>
+      </c>
+      <c r="D90">
+        <v>90</v>
+      </c>
+      <c r="E90" t="s">
+        <v>538</v>
+      </c>
+      <c r="F90" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca90.jpg</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>403</v>
+      </c>
+      <c r="C91" t="s">
+        <v>537</v>
+      </c>
+      <c r="D91">
+        <v>91</v>
+      </c>
+      <c r="E91" t="s">
+        <v>538</v>
+      </c>
+      <c r="F91" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca91.jpg</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>404</v>
+      </c>
+      <c r="C92" t="s">
+        <v>537</v>
+      </c>
+      <c r="D92">
+        <v>92</v>
+      </c>
+      <c r="E92" t="s">
+        <v>538</v>
+      </c>
+      <c r="F92" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca92.jpg</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>405</v>
+      </c>
+      <c r="C93" t="s">
+        <v>537</v>
+      </c>
+      <c r="D93">
+        <v>93</v>
+      </c>
+      <c r="E93" t="s">
+        <v>538</v>
+      </c>
+      <c r="F93" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca93.jpg</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>406</v>
+      </c>
+      <c r="C94" t="s">
+        <v>537</v>
+      </c>
+      <c r="D94">
+        <v>94</v>
+      </c>
+      <c r="E94" t="s">
+        <v>538</v>
+      </c>
+      <c r="F94" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca94.jpg</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>407</v>
+      </c>
+      <c r="C95" t="s">
+        <v>537</v>
+      </c>
+      <c r="D95">
+        <v>95</v>
+      </c>
+      <c r="E95" t="s">
+        <v>538</v>
+      </c>
+      <c r="F95" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca95.jpg</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>408</v>
+      </c>
+      <c r="C96" t="s">
+        <v>537</v>
+      </c>
+      <c r="D96">
+        <v>96</v>
+      </c>
+      <c r="E96" t="s">
+        <v>538</v>
+      </c>
+      <c r="F96" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca96.jpg</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>409</v>
+      </c>
+      <c r="C97" t="s">
+        <v>537</v>
+      </c>
+      <c r="D97">
+        <v>97</v>
+      </c>
+      <c r="E97" t="s">
+        <v>538</v>
+      </c>
+      <c r="F97" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca97.jpg</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>410</v>
+      </c>
+      <c r="C98" t="s">
+        <v>537</v>
+      </c>
+      <c r="D98">
+        <v>98</v>
+      </c>
+      <c r="E98" t="s">
+        <v>538</v>
+      </c>
+      <c r="F98" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca98.jpg</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>411</v>
+      </c>
+      <c r="C99" t="s">
+        <v>537</v>
+      </c>
+      <c r="D99">
+        <v>99</v>
+      </c>
+      <c r="E99" t="s">
+        <v>538</v>
+      </c>
+      <c r="F99" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca99.jpg</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>412</v>
+      </c>
+      <c r="C100" t="s">
+        <v>537</v>
+      </c>
+      <c r="D100">
+        <v>100</v>
+      </c>
+      <c r="E100" t="s">
+        <v>538</v>
+      </c>
+      <c r="F100" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca100.jpg</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>413</v>
+      </c>
+      <c r="C101" t="s">
+        <v>537</v>
+      </c>
+      <c r="D101">
+        <v>101</v>
+      </c>
+      <c r="E101" t="s">
+        <v>538</v>
+      </c>
+      <c r="F101" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca101.jpg</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>414</v>
+      </c>
+      <c r="C102" t="s">
+        <v>537</v>
+      </c>
+      <c r="D102">
+        <v>102</v>
+      </c>
+      <c r="E102" t="s">
+        <v>538</v>
+      </c>
+      <c r="F102" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca102.jpg</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>415</v>
+      </c>
+      <c r="C103" t="s">
+        <v>537</v>
+      </c>
+      <c r="D103">
+        <v>103</v>
+      </c>
+      <c r="E103" t="s">
+        <v>538</v>
+      </c>
+      <c r="F103" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca103.jpg</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>416</v>
+      </c>
+      <c r="C104" t="s">
+        <v>537</v>
+      </c>
+      <c r="D104">
+        <v>104</v>
+      </c>
+      <c r="E104" t="s">
+        <v>538</v>
+      </c>
+      <c r="F104" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca104.jpg</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>417</v>
+      </c>
+      <c r="C105" t="s">
+        <v>537</v>
+      </c>
+      <c r="D105">
+        <v>105</v>
+      </c>
+      <c r="E105" t="s">
+        <v>538</v>
+      </c>
+      <c r="F105" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca105.jpg</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>418</v>
+      </c>
+      <c r="C106" t="s">
+        <v>537</v>
+      </c>
+      <c r="D106">
+        <v>106</v>
+      </c>
+      <c r="E106" t="s">
+        <v>538</v>
+      </c>
+      <c r="F106" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca106.jpg</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>419</v>
+      </c>
+      <c r="C107" t="s">
+        <v>537</v>
+      </c>
+      <c r="D107">
+        <v>107</v>
+      </c>
+      <c r="E107" t="s">
+        <v>538</v>
+      </c>
+      <c r="F107" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca107.jpg</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>420</v>
+      </c>
+      <c r="C108" t="s">
+        <v>537</v>
+      </c>
+      <c r="D108">
+        <v>108</v>
+      </c>
+      <c r="E108" t="s">
+        <v>538</v>
+      </c>
+      <c r="F108" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca108.jpg</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>421</v>
+      </c>
+      <c r="C109" t="s">
+        <v>537</v>
+      </c>
+      <c r="D109">
+        <v>109</v>
+      </c>
+      <c r="E109" t="s">
+        <v>538</v>
+      </c>
+      <c r="F109" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca109.jpg</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>422</v>
+      </c>
+      <c r="C110" t="s">
+        <v>537</v>
+      </c>
+      <c r="D110">
+        <v>110</v>
+      </c>
+      <c r="E110" t="s">
+        <v>538</v>
+      </c>
+      <c r="F110" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca110.jpg</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>423</v>
+      </c>
+      <c r="C111" t="s">
+        <v>537</v>
+      </c>
+      <c r="D111">
+        <v>111</v>
+      </c>
+      <c r="E111" t="s">
+        <v>538</v>
+      </c>
+      <c r="F111" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca111.jpg</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>424</v>
+      </c>
+      <c r="C112" t="s">
+        <v>537</v>
+      </c>
+      <c r="D112">
+        <v>112</v>
+      </c>
+      <c r="E112" t="s">
+        <v>538</v>
+      </c>
+      <c r="F112" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca112.jpg</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>425</v>
+      </c>
+      <c r="C113" t="s">
+        <v>537</v>
+      </c>
+      <c r="D113">
+        <v>113</v>
+      </c>
+      <c r="E113" t="s">
+        <v>538</v>
+      </c>
+      <c r="F113" t="str">
+        <f t="shared" si="1"/>
+        <v>img/coleccionables/ca113.jpg</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/catalogo_productos.xlsx
+++ b/data/catalogo_productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ndrsb\Documents\Mimitos\Mimitos\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735280F6-6560-487C-869E-3AEF382133DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E24B8BD-877D-4E11-A076-AD16CEE1B191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1694,9 +1694,6 @@
     <t>img/llaveros/k45.jpeg</t>
   </si>
   <si>
-    <t>img/llaveros/k46.jpeg</t>
-  </si>
-  <si>
     <t>img/llaveros/k47.jpeg</t>
   </si>
   <si>
@@ -2358,6 +2355,9 @@
   </si>
   <si>
     <t>img/didacticos/d16.jpeg;img/didacticos/d16_1.jpeg;img/didacticos/d16_2.jpeg</t>
+  </si>
+  <si>
+    <t>img/llaveros/k46.jpeg;img/llaveros/k46_2.jpeg</t>
   </si>
 </sst>
 </file>
@@ -4095,7 +4095,7 @@
         <v>219</v>
       </c>
       <c r="B47" t="s">
-        <v>551</v>
+        <v>772</v>
       </c>
       <c r="C47" t="s">
         <v>76</v>
@@ -4124,7 +4124,7 @@
         <v>219</v>
       </c>
       <c r="B48" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C48" t="s">
         <v>81</v>
@@ -4153,7 +4153,7 @@
         <v>219</v>
       </c>
       <c r="B49" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C49" t="s">
         <v>85</v>
@@ -4182,7 +4182,7 @@
         <v>219</v>
       </c>
       <c r="B50" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C50" t="s">
         <v>90</v>
@@ -4211,7 +4211,7 @@
         <v>219</v>
       </c>
       <c r="B51" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C51" t="s">
         <v>95</v>
@@ -4240,7 +4240,7 @@
         <v>219</v>
       </c>
       <c r="B52" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C52" t="s">
         <v>99</v>
@@ -4269,7 +4269,7 @@
         <v>219</v>
       </c>
       <c r="B53" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C53" t="s">
         <v>76</v>
@@ -4298,7 +4298,7 @@
         <v>219</v>
       </c>
       <c r="B54" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C54" t="s">
         <v>81</v>
@@ -4327,7 +4327,7 @@
         <v>219</v>
       </c>
       <c r="B55" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C55" t="s">
         <v>85</v>
@@ -4356,7 +4356,7 @@
         <v>219</v>
       </c>
       <c r="B56" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C56" t="s">
         <v>90</v>
@@ -4386,7 +4386,7 @@
         <v>219</v>
       </c>
       <c r="B57" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C57" t="s">
         <v>95</v>
@@ -4415,7 +4415,7 @@
         <v>220</v>
       </c>
       <c r="B58" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C58" t="s">
         <v>119</v>
@@ -4444,7 +4444,7 @@
         <v>220</v>
       </c>
       <c r="B59" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C59" t="s">
         <v>124</v>
@@ -4476,7 +4476,7 @@
         <v>220</v>
       </c>
       <c r="B60" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C60" t="s">
         <v>129</v>
@@ -4505,7 +4505,7 @@
         <v>220</v>
       </c>
       <c r="B61" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C61" t="s">
         <v>134</v>
@@ -4537,7 +4537,7 @@
         <v>220</v>
       </c>
       <c r="B62" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C62" t="s">
         <v>139</v>
@@ -4566,7 +4566,7 @@
         <v>220</v>
       </c>
       <c r="B63" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C63" t="s">
         <v>144</v>
@@ -4598,7 +4598,7 @@
         <v>220</v>
       </c>
       <c r="B64" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C64" t="s">
         <v>149</v>
@@ -4627,7 +4627,7 @@
         <v>220</v>
       </c>
       <c r="B65" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C65" t="s">
         <v>154</v>
@@ -4656,7 +4656,7 @@
         <v>220</v>
       </c>
       <c r="B66" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C66" t="s">
         <v>159</v>
@@ -4685,7 +4685,7 @@
         <v>220</v>
       </c>
       <c r="B67" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C67" t="s">
         <v>164</v>
@@ -4714,7 +4714,7 @@
         <v>220</v>
       </c>
       <c r="B68" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C68" t="s">
         <v>169</v>
@@ -4743,7 +4743,7 @@
         <v>220</v>
       </c>
       <c r="B69" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C69" t="s">
         <v>174</v>
@@ -4775,7 +4775,7 @@
         <v>220</v>
       </c>
       <c r="B70" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C70" t="s">
         <v>179</v>
@@ -4804,7 +4804,7 @@
         <v>220</v>
       </c>
       <c r="B71" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C71" t="s">
         <v>184</v>
@@ -4833,7 +4833,7 @@
         <v>220</v>
       </c>
       <c r="B72" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C72" t="s">
         <v>189</v>
@@ -4862,7 +4862,7 @@
         <v>220</v>
       </c>
       <c r="B73" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C73" t="s">
         <v>194</v>
@@ -4891,7 +4891,7 @@
         <v>220</v>
       </c>
       <c r="B74" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C74" t="s">
         <v>199</v>
@@ -4923,7 +4923,7 @@
         <v>220</v>
       </c>
       <c r="B75" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C75" t="s">
         <v>204</v>
@@ -4952,7 +4952,7 @@
         <v>220</v>
       </c>
       <c r="B76" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C76" t="s">
         <v>209</v>
@@ -4981,7 +4981,7 @@
         <v>220</v>
       </c>
       <c r="B77" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C77" t="s">
         <v>214</v>
@@ -5016,7 +5016,7 @@
         <v>337</v>
       </c>
       <c r="C78" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D78">
         <v>20000</v>
@@ -5031,13 +5031,13 @@
         <v>11</v>
       </c>
       <c r="H78" t="s">
+        <v>562</v>
+      </c>
+      <c r="I78" t="s">
         <v>563</v>
       </c>
-      <c r="I78" t="s">
+      <c r="J78" t="s">
         <v>564</v>
-      </c>
-      <c r="J78" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -5048,7 +5048,7 @@
         <v>338</v>
       </c>
       <c r="C79" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D79">
         <v>800</v>
@@ -5063,13 +5063,13 @@
         <v>47</v>
       </c>
       <c r="H79" t="s">
+        <v>566</v>
+      </c>
+      <c r="I79" t="s">
         <v>567</v>
       </c>
-      <c r="I79" t="s">
-        <v>568</v>
-      </c>
       <c r="J79" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -5080,7 +5080,7 @@
         <v>339</v>
       </c>
       <c r="C80" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D80">
         <v>2000</v>
@@ -5092,10 +5092,10 @@
         <v>1</v>
       </c>
       <c r="H80" t="s">
+        <v>569</v>
+      </c>
+      <c r="J80" t="s">
         <v>570</v>
-      </c>
-      <c r="J80" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -5106,7 +5106,7 @@
         <v>340</v>
       </c>
       <c r="C81" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D81">
         <v>12000</v>
@@ -5118,13 +5118,13 @@
         <v>1</v>
       </c>
       <c r="H81" t="s">
+        <v>572</v>
+      </c>
+      <c r="I81" t="s">
         <v>573</v>
       </c>
-      <c r="I81" t="s">
+      <c r="J81" t="s">
         <v>574</v>
-      </c>
-      <c r="J81" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
@@ -5135,7 +5135,7 @@
         <v>341</v>
       </c>
       <c r="C82" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D82">
         <v>12000</v>
@@ -5147,13 +5147,13 @@
         <v>1</v>
       </c>
       <c r="H82" t="s">
+        <v>572</v>
+      </c>
+      <c r="I82" t="s">
         <v>573</v>
       </c>
-      <c r="I82" t="s">
+      <c r="J82" t="s">
         <v>574</v>
-      </c>
-      <c r="J82" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
@@ -5164,7 +5164,7 @@
         <v>342</v>
       </c>
       <c r="C83" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D83">
         <v>12000</v>
@@ -5176,13 +5176,13 @@
         <v>1</v>
       </c>
       <c r="H83" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I83" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J83" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
@@ -5193,7 +5193,7 @@
         <v>343</v>
       </c>
       <c r="C84" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D84">
         <v>12000</v>
@@ -5205,13 +5205,13 @@
         <v>1</v>
       </c>
       <c r="H84" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I84" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="J84" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
@@ -5222,7 +5222,7 @@
         <v>344</v>
       </c>
       <c r="C85" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D85">
         <v>12000</v>
@@ -5237,13 +5237,13 @@
         <v>47</v>
       </c>
       <c r="H85" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I85" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="J85" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
@@ -5254,7 +5254,7 @@
         <v>345</v>
       </c>
       <c r="C86" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D86">
         <v>12000</v>
@@ -5266,13 +5266,13 @@
         <v>1</v>
       </c>
       <c r="H86" t="s">
+        <v>572</v>
+      </c>
+      <c r="I86" t="s">
         <v>573</v>
       </c>
-      <c r="I86" t="s">
+      <c r="J86" t="s">
         <v>574</v>
-      </c>
-      <c r="J86" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
@@ -5283,7 +5283,7 @@
         <v>346</v>
       </c>
       <c r="C87" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D87">
         <v>12000</v>
@@ -5298,13 +5298,13 @@
         <v>58</v>
       </c>
       <c r="H87" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I87" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="J87" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
@@ -5315,7 +5315,7 @@
         <v>347</v>
       </c>
       <c r="C88" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D88">
         <v>12000</v>
@@ -5327,13 +5327,13 @@
         <v>1</v>
       </c>
       <c r="H88" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I88" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="J88" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
@@ -5344,7 +5344,7 @@
         <v>348</v>
       </c>
       <c r="C89" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D89">
         <v>12000</v>
@@ -5359,13 +5359,13 @@
         <v>27</v>
       </c>
       <c r="H89" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I89" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="J89" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
@@ -5376,7 +5376,7 @@
         <v>349</v>
       </c>
       <c r="C90" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D90">
         <v>12000</v>
@@ -5388,13 +5388,13 @@
         <v>1</v>
       </c>
       <c r="H90" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I90" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="J90" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
@@ -5405,7 +5405,7 @@
         <v>350</v>
       </c>
       <c r="C91" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D91">
         <v>12000</v>
@@ -5417,13 +5417,13 @@
         <v>1</v>
       </c>
       <c r="H91" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I91" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="J91" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
@@ -5434,7 +5434,7 @@
         <v>351</v>
       </c>
       <c r="C92" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D92">
         <v>12000</v>
@@ -5446,13 +5446,13 @@
         <v>1</v>
       </c>
       <c r="H92" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I92" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="J92" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
@@ -5463,7 +5463,7 @@
         <v>352</v>
       </c>
       <c r="C93" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D93">
         <v>12000</v>
@@ -5475,13 +5475,13 @@
         <v>1</v>
       </c>
       <c r="H93" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I93" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="J93" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
@@ -5492,7 +5492,7 @@
         <v>353</v>
       </c>
       <c r="C94" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D94">
         <v>14000</v>
@@ -5504,13 +5504,13 @@
         <v>1</v>
       </c>
       <c r="H94" t="s">
+        <v>595</v>
+      </c>
+      <c r="I94" t="s">
         <v>596</v>
       </c>
-      <c r="I94" t="s">
-        <v>597</v>
-      </c>
       <c r="J94" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
@@ -5521,7 +5521,7 @@
         <v>354</v>
       </c>
       <c r="C95" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D95">
         <v>14000</v>
@@ -5533,13 +5533,13 @@
         <v>1</v>
       </c>
       <c r="H95" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I95" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J95" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
@@ -5550,7 +5550,7 @@
         <v>355</v>
       </c>
       <c r="C96" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D96">
         <v>14000</v>
@@ -5562,13 +5562,13 @@
         <v>1</v>
       </c>
       <c r="H96" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I96" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J96" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
@@ -5579,7 +5579,7 @@
         <v>356</v>
       </c>
       <c r="C97" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D97">
         <v>14000</v>
@@ -5594,13 +5594,13 @@
         <v>47</v>
       </c>
       <c r="H97" t="s">
+        <v>595</v>
+      </c>
+      <c r="I97" t="s">
         <v>596</v>
       </c>
-      <c r="I97" t="s">
-        <v>597</v>
-      </c>
       <c r="J97" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
@@ -5611,7 +5611,7 @@
         <v>357</v>
       </c>
       <c r="C98" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D98">
         <v>14000</v>
@@ -5626,13 +5626,13 @@
         <v>27</v>
       </c>
       <c r="H98" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I98" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="J98" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -5643,7 +5643,7 @@
         <v>358</v>
       </c>
       <c r="C99" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D99">
         <v>14000</v>
@@ -5655,13 +5655,13 @@
         <v>1</v>
       </c>
       <c r="H99" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I99" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="J99" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -5672,7 +5672,7 @@
         <v>359</v>
       </c>
       <c r="C100" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D100">
         <v>35000</v>
@@ -5684,13 +5684,13 @@
         <v>1</v>
       </c>
       <c r="H100" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I100" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="J100" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -5701,7 +5701,7 @@
         <v>360</v>
       </c>
       <c r="C101" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D101">
         <v>35000</v>
@@ -5713,13 +5713,13 @@
         <v>1</v>
       </c>
       <c r="H101" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I101" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="J101" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -5730,7 +5730,7 @@
         <v>361</v>
       </c>
       <c r="C102" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D102">
         <v>35000</v>
@@ -5745,13 +5745,13 @@
         <v>47</v>
       </c>
       <c r="H102" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I102" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="J102" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
@@ -5762,7 +5762,7 @@
         <v>362</v>
       </c>
       <c r="C103" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D103">
         <v>35000</v>
@@ -5774,13 +5774,13 @@
         <v>1</v>
       </c>
       <c r="H103" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I103" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="J103" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -5791,7 +5791,7 @@
         <v>363</v>
       </c>
       <c r="C104" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D104">
         <v>45000</v>
@@ -5803,13 +5803,13 @@
         <v>1</v>
       </c>
       <c r="H104" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I104" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J104" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -5820,7 +5820,7 @@
         <v>364</v>
       </c>
       <c r="C105" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D105">
         <v>45000</v>
@@ -5832,13 +5832,13 @@
         <v>1</v>
       </c>
       <c r="H105" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I105" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="J105" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
@@ -5849,7 +5849,7 @@
         <v>365</v>
       </c>
       <c r="C106" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D106">
         <v>45000</v>
@@ -5861,10 +5861,10 @@
         <v>1</v>
       </c>
       <c r="H106" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I106" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="J106" t="s">
         <v>106</v>
@@ -5878,7 +5878,7 @@
         <v>366</v>
       </c>
       <c r="C107" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D107">
         <v>45000</v>
@@ -5893,10 +5893,10 @@
         <v>11</v>
       </c>
       <c r="H107" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I107" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J107" t="s">
         <v>107</v>
@@ -5910,7 +5910,7 @@
         <v>367</v>
       </c>
       <c r="C108" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D108">
         <v>30000</v>
@@ -5922,10 +5922,10 @@
         <v>1</v>
       </c>
       <c r="H108" t="s">
+        <v>620</v>
+      </c>
+      <c r="I108" t="s">
         <v>621</v>
-      </c>
-      <c r="I108" t="s">
-        <v>622</v>
       </c>
       <c r="J108" t="s">
         <v>108</v>
@@ -5939,7 +5939,7 @@
         <v>368</v>
       </c>
       <c r="C109" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D109">
         <v>30000</v>
@@ -5954,10 +5954,10 @@
         <v>27</v>
       </c>
       <c r="H109" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I109" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="J109" t="s">
         <v>109</v>
@@ -5971,7 +5971,7 @@
         <v>369</v>
       </c>
       <c r="C110" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D110">
         <v>30000</v>
@@ -5983,10 +5983,10 @@
         <v>1</v>
       </c>
       <c r="H110" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I110" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="J110" t="s">
         <v>110</v>
@@ -6000,7 +6000,7 @@
         <v>370</v>
       </c>
       <c r="C111" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D111">
         <v>30000</v>
@@ -6012,10 +6012,10 @@
         <v>1</v>
       </c>
       <c r="H111" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I111" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J111" t="s">
         <v>111</v>
@@ -6029,7 +6029,7 @@
         <v>371</v>
       </c>
       <c r="C112" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D112">
         <v>30000</v>
@@ -6041,10 +6041,10 @@
         <v>1</v>
       </c>
       <c r="H112" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I112" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="J112" t="s">
         <v>112</v>
@@ -6058,7 +6058,7 @@
         <v>372</v>
       </c>
       <c r="C113" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D113">
         <v>30000</v>
@@ -6070,10 +6070,10 @@
         <v>1</v>
       </c>
       <c r="H113" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I113" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="J113" t="s">
         <v>113</v>
@@ -6087,7 +6087,7 @@
         <v>373</v>
       </c>
       <c r="C114" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D114">
         <v>30000</v>
@@ -6102,10 +6102,10 @@
         <v>47</v>
       </c>
       <c r="H114" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I114" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="J114" t="s">
         <v>114</v>
@@ -6119,7 +6119,7 @@
         <v>374</v>
       </c>
       <c r="C115" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D115">
         <v>30000</v>
@@ -6131,10 +6131,10 @@
         <v>1</v>
       </c>
       <c r="H115" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I115" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="J115" t="s">
         <v>115</v>
@@ -6148,7 +6148,7 @@
         <v>375</v>
       </c>
       <c r="C116" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D116">
         <v>30000</v>
@@ -6163,10 +6163,10 @@
         <v>11</v>
       </c>
       <c r="H116" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I116" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="J116" t="s">
         <v>116</v>
@@ -6180,7 +6180,7 @@
         <v>376</v>
       </c>
       <c r="C117" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D117">
         <v>30000</v>
@@ -6192,10 +6192,10 @@
         <v>1</v>
       </c>
       <c r="H117" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I117" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="J117" t="s">
         <v>117</v>
@@ -6209,7 +6209,7 @@
         <v>377</v>
       </c>
       <c r="C118" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D118">
         <v>30000</v>
@@ -6221,10 +6221,10 @@
         <v>1</v>
       </c>
       <c r="H118" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I118" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="J118" t="s">
         <v>122</v>
@@ -6238,7 +6238,7 @@
         <v>378</v>
       </c>
       <c r="C119" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D119">
         <v>30000</v>
@@ -6253,10 +6253,10 @@
         <v>47</v>
       </c>
       <c r="H119" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I119" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="J119" t="s">
         <v>127</v>
@@ -6270,7 +6270,7 @@
         <v>379</v>
       </c>
       <c r="C120" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D120">
         <v>30000</v>
@@ -6282,10 +6282,10 @@
         <v>1</v>
       </c>
       <c r="H120" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I120" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="J120" t="s">
         <v>132</v>
@@ -6299,7 +6299,7 @@
         <v>380</v>
       </c>
       <c r="C121" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D121">
         <v>40000</v>
@@ -6314,10 +6314,10 @@
         <v>11</v>
       </c>
       <c r="H121" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="I121" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J121" t="s">
         <v>137</v>
@@ -6331,7 +6331,7 @@
         <v>381</v>
       </c>
       <c r="C122" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D122">
         <v>25000</v>
@@ -6343,10 +6343,10 @@
         <v>1</v>
       </c>
       <c r="H122" t="s">
+        <v>645</v>
+      </c>
+      <c r="I122" t="s">
         <v>646</v>
-      </c>
-      <c r="I122" t="s">
-        <v>647</v>
       </c>
       <c r="J122" t="s">
         <v>142</v>
@@ -6360,7 +6360,7 @@
         <v>382</v>
       </c>
       <c r="C123" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D123">
         <v>25000</v>
@@ -6375,10 +6375,10 @@
         <v>27</v>
       </c>
       <c r="H123" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="I123" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J123" t="s">
         <v>147</v>
@@ -6392,7 +6392,7 @@
         <v>383</v>
       </c>
       <c r="C124" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D124">
         <v>25000</v>
@@ -6404,10 +6404,10 @@
         <v>1</v>
       </c>
       <c r="H124" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="I124" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="J124" t="s">
         <v>152</v>
@@ -6421,7 +6421,7 @@
         <v>384</v>
       </c>
       <c r="C125" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D125">
         <v>25000</v>
@@ -6433,10 +6433,10 @@
         <v>1</v>
       </c>
       <c r="H125" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="I125" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="J125" t="s">
         <v>157</v>
@@ -6450,7 +6450,7 @@
         <v>385</v>
       </c>
       <c r="C126" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D126">
         <v>18000</v>
@@ -6462,10 +6462,10 @@
         <v>1</v>
       </c>
       <c r="H126" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I126" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="J126" t="s">
         <v>162</v>
@@ -6479,7 +6479,7 @@
         <v>386</v>
       </c>
       <c r="C127" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D127">
         <v>18000</v>
@@ -6491,10 +6491,10 @@
         <v>1</v>
       </c>
       <c r="H127" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I127" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J127" t="s">
         <v>167</v>
@@ -6508,7 +6508,7 @@
         <v>387</v>
       </c>
       <c r="C128" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D128">
         <v>18000</v>
@@ -6520,10 +6520,10 @@
         <v>1</v>
       </c>
       <c r="H128" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I128" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="J128" t="s">
         <v>172</v>
@@ -6537,7 +6537,7 @@
         <v>388</v>
       </c>
       <c r="C129" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D129">
         <v>18000</v>
@@ -6552,10 +6552,10 @@
         <v>47</v>
       </c>
       <c r="H129" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="I129" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J129" t="s">
         <v>177</v>
@@ -6569,7 +6569,7 @@
         <v>389</v>
       </c>
       <c r="C130" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D130">
         <v>15000</v>
@@ -6581,10 +6581,10 @@
         <v>1</v>
       </c>
       <c r="H130" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="I130" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="J130" t="s">
         <v>182</v>
@@ -6598,7 +6598,7 @@
         <v>390</v>
       </c>
       <c r="C131" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D131">
         <v>15000</v>
@@ -6610,10 +6610,10 @@
         <v>1</v>
       </c>
       <c r="H131" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="I131" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J131" t="s">
         <v>187</v>
@@ -6627,7 +6627,7 @@
         <v>391</v>
       </c>
       <c r="C132" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D132">
         <v>15000</v>
@@ -6639,10 +6639,10 @@
         <v>1</v>
       </c>
       <c r="H132" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="I132" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="J132" t="s">
         <v>192</v>
@@ -6656,7 +6656,7 @@
         <v>392</v>
       </c>
       <c r="C133" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D133">
         <v>15000</v>
@@ -6668,10 +6668,10 @@
         <v>1</v>
       </c>
       <c r="H133" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="I133" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="J133" t="s">
         <v>197</v>
@@ -6685,7 +6685,7 @@
         <v>393</v>
       </c>
       <c r="C134" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D134">
         <v>15000</v>
@@ -6700,10 +6700,10 @@
         <v>11</v>
       </c>
       <c r="H134" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="I134" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="J134" t="s">
         <v>202</v>
@@ -6717,7 +6717,7 @@
         <v>394</v>
       </c>
       <c r="C135" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D135">
         <v>15000</v>
@@ -6729,10 +6729,10 @@
         <v>1</v>
       </c>
       <c r="H135" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="I135" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="J135" t="s">
         <v>207</v>
@@ -6746,7 +6746,7 @@
         <v>395</v>
       </c>
       <c r="C136" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D136">
         <v>15000</v>
@@ -6758,10 +6758,10 @@
         <v>1</v>
       </c>
       <c r="H136" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="I136" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="J136" t="s">
         <v>212</v>
@@ -6775,7 +6775,7 @@
         <v>396</v>
       </c>
       <c r="C137" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D137">
         <v>15000</v>
@@ -6790,10 +6790,10 @@
         <v>27</v>
       </c>
       <c r="H137" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="I137" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="J137" t="s">
         <v>109</v>
@@ -6807,7 +6807,7 @@
         <v>397</v>
       </c>
       <c r="C138" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D138">
         <v>15000</v>
@@ -6819,10 +6819,10 @@
         <v>1</v>
       </c>
       <c r="H138" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="I138" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="J138" t="s">
         <v>110</v>
@@ -6836,7 +6836,7 @@
         <v>398</v>
       </c>
       <c r="C139" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D139">
         <v>15000</v>
@@ -6848,10 +6848,10 @@
         <v>1</v>
       </c>
       <c r="H139" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="I139" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="J139" t="s">
         <v>111</v>
@@ -6865,7 +6865,7 @@
         <v>399</v>
       </c>
       <c r="C140" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D140">
         <v>15000</v>
@@ -6877,10 +6877,10 @@
         <v>1</v>
       </c>
       <c r="H140" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="I140" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="J140" t="s">
         <v>112</v>
@@ -6894,7 +6894,7 @@
         <v>400</v>
       </c>
       <c r="C141" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D141">
         <v>15000</v>
@@ -6906,10 +6906,10 @@
         <v>1</v>
       </c>
       <c r="H141" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="I141" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="J141" t="s">
         <v>113</v>
@@ -6923,7 +6923,7 @@
         <v>401</v>
       </c>
       <c r="C142" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D142">
         <v>18000</v>
@@ -6935,10 +6935,10 @@
         <v>1</v>
       </c>
       <c r="H142" t="s">
+        <v>677</v>
+      </c>
+      <c r="I142" t="s">
         <v>678</v>
-      </c>
-      <c r="I142" t="s">
-        <v>679</v>
       </c>
       <c r="J142" t="s">
         <v>114</v>
@@ -6952,7 +6952,7 @@
         <v>402</v>
       </c>
       <c r="C143" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D143">
         <v>18000</v>
@@ -6964,10 +6964,10 @@
         <v>1</v>
       </c>
       <c r="H143" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="I143" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="J143" t="s">
         <v>115</v>
@@ -6981,7 +6981,7 @@
         <v>403</v>
       </c>
       <c r="C144" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D144">
         <v>18000</v>
@@ -6993,10 +6993,10 @@
         <v>1</v>
       </c>
       <c r="H144" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="I144" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="J144" t="s">
         <v>116</v>
@@ -7010,7 +7010,7 @@
         <v>404</v>
       </c>
       <c r="C145" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D145">
         <v>18000</v>
@@ -7022,10 +7022,10 @@
         <v>1</v>
       </c>
       <c r="H145" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="I145" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="J145" t="s">
         <v>117</v>
@@ -7039,7 +7039,7 @@
         <v>405</v>
       </c>
       <c r="C146" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D146">
         <v>18000</v>
@@ -7051,10 +7051,10 @@
         <v>1</v>
       </c>
       <c r="H146" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="I146" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="J146" t="s">
         <v>122</v>
@@ -7068,7 +7068,7 @@
         <v>406</v>
       </c>
       <c r="C147" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D147">
         <v>18000</v>
@@ -7080,10 +7080,10 @@
         <v>1</v>
       </c>
       <c r="H147" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="I147" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J147" t="s">
         <v>127</v>
@@ -7097,7 +7097,7 @@
         <v>407</v>
       </c>
       <c r="C148" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D148">
         <v>18000</v>
@@ -7109,10 +7109,10 @@
         <v>1</v>
       </c>
       <c r="H148" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="I148" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="J148" t="s">
         <v>132</v>
@@ -7126,7 +7126,7 @@
         <v>408</v>
       </c>
       <c r="C149" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D149">
         <v>18000</v>
@@ -7138,10 +7138,10 @@
         <v>1</v>
       </c>
       <c r="H149" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="I149" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="J149" t="s">
         <v>137</v>
@@ -7155,7 +7155,7 @@
         <v>409</v>
       </c>
       <c r="C150" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D150">
         <v>15000</v>
@@ -7167,10 +7167,10 @@
         <v>1</v>
       </c>
       <c r="H150" t="s">
+        <v>692</v>
+      </c>
+      <c r="I150" t="s">
         <v>693</v>
-      </c>
-      <c r="I150" t="s">
-        <v>694</v>
       </c>
       <c r="J150" t="s">
         <v>142</v>
@@ -7184,7 +7184,7 @@
         <v>410</v>
       </c>
       <c r="C151" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D151">
         <v>25000</v>
@@ -7196,10 +7196,10 @@
         <v>1</v>
       </c>
       <c r="H151" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="I151" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="J151" t="s">
         <v>147</v>
@@ -7213,7 +7213,7 @@
         <v>411</v>
       </c>
       <c r="C152" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D152">
         <v>15000</v>
@@ -7225,10 +7225,10 @@
         <v>1</v>
       </c>
       <c r="H152" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="I152" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="J152" t="s">
         <v>152</v>
@@ -7242,7 +7242,7 @@
         <v>412</v>
       </c>
       <c r="C153" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D153">
         <v>15000</v>
@@ -7254,10 +7254,10 @@
         <v>1</v>
       </c>
       <c r="H153" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="I153" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="J153" t="s">
         <v>157</v>
@@ -7271,7 +7271,7 @@
         <v>413</v>
       </c>
       <c r="C154" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D154">
         <v>25000</v>
@@ -7283,10 +7283,10 @@
         <v>1</v>
       </c>
       <c r="H154" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="I154" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="J154" t="s">
         <v>162</v>
@@ -7300,7 +7300,7 @@
         <v>414</v>
       </c>
       <c r="C155" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D155">
         <v>20000</v>
@@ -7312,10 +7312,10 @@
         <v>1</v>
       </c>
       <c r="H155" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="I155" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="J155" t="s">
         <v>167</v>
@@ -7329,7 +7329,7 @@
         <v>415</v>
       </c>
       <c r="C156" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D156">
         <v>20000</v>
@@ -7341,10 +7341,10 @@
         <v>1</v>
       </c>
       <c r="H156" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="I156" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="J156" t="s">
         <v>172</v>
@@ -7358,7 +7358,7 @@
         <v>416</v>
       </c>
       <c r="C157" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D157">
         <v>15000</v>
@@ -7370,10 +7370,10 @@
         <v>1</v>
       </c>
       <c r="H157" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="I157" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="J157" t="s">
         <v>177</v>
@@ -7387,7 +7387,7 @@
         <v>417</v>
       </c>
       <c r="C158" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D158">
         <v>25000</v>
@@ -7399,10 +7399,10 @@
         <v>1</v>
       </c>
       <c r="H158" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="I158" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="J158" t="s">
         <v>182</v>
@@ -7416,7 +7416,7 @@
         <v>418</v>
       </c>
       <c r="C159" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D159">
         <v>25000</v>
@@ -7428,10 +7428,10 @@
         <v>1</v>
       </c>
       <c r="H159" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="I159" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="J159" t="s">
         <v>187</v>
@@ -7445,7 +7445,7 @@
         <v>419</v>
       </c>
       <c r="C160" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D160">
         <v>25000</v>
@@ -7457,10 +7457,10 @@
         <v>1</v>
       </c>
       <c r="H160" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="I160" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="J160" t="s">
         <v>192</v>
@@ -7474,7 +7474,7 @@
         <v>420</v>
       </c>
       <c r="C161" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D161">
         <v>25000</v>
@@ -7486,10 +7486,10 @@
         <v>1</v>
       </c>
       <c r="H161" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="I161" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="J161" t="s">
         <v>197</v>
@@ -7503,7 +7503,7 @@
         <v>421</v>
       </c>
       <c r="C162" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D162">
         <v>25000</v>
@@ -7515,10 +7515,10 @@
         <v>1</v>
       </c>
       <c r="H162" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="I162" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="J162" t="s">
         <v>202</v>
@@ -7532,7 +7532,7 @@
         <v>422</v>
       </c>
       <c r="C163" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D163">
         <v>25000</v>
@@ -7544,10 +7544,10 @@
         <v>1</v>
       </c>
       <c r="H163" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="I163" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="J163" t="s">
         <v>207</v>
@@ -7561,7 +7561,7 @@
         <v>423</v>
       </c>
       <c r="C164" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D164">
         <v>25000</v>
@@ -7573,10 +7573,10 @@
         <v>1</v>
       </c>
       <c r="H164" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I164" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="J164" t="s">
         <v>212</v>
@@ -7590,7 +7590,7 @@
         <v>424</v>
       </c>
       <c r="C165" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D165">
         <v>25000</v>
@@ -7602,10 +7602,10 @@
         <v>1</v>
       </c>
       <c r="H165" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I165" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
@@ -7616,7 +7616,7 @@
         <v>425</v>
       </c>
       <c r="C166" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D166">
         <v>25000</v>
@@ -7628,10 +7628,10 @@
         <v>1</v>
       </c>
       <c r="H166" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I166" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
@@ -7642,7 +7642,7 @@
         <v>426</v>
       </c>
       <c r="C167" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D167">
         <v>25000</v>
@@ -7654,10 +7654,10 @@
         <v>1</v>
       </c>
       <c r="H167" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="I167" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
@@ -7668,7 +7668,7 @@
         <v>427</v>
       </c>
       <c r="C168" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D168">
         <v>27000</v>
@@ -7680,10 +7680,10 @@
         <v>1</v>
       </c>
       <c r="H168" t="s">
+        <v>719</v>
+      </c>
+      <c r="I168" t="s">
         <v>720</v>
-      </c>
-      <c r="I168" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
@@ -7694,7 +7694,7 @@
         <v>428</v>
       </c>
       <c r="C169" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D169">
         <v>27000</v>
@@ -7706,10 +7706,10 @@
         <v>1</v>
       </c>
       <c r="H169" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="I169" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
@@ -7720,7 +7720,7 @@
         <v>429</v>
       </c>
       <c r="C170" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D170">
         <v>27000</v>
@@ -7732,10 +7732,10 @@
         <v>1</v>
       </c>
       <c r="H170" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="I170" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
@@ -7746,7 +7746,7 @@
         <v>430</v>
       </c>
       <c r="C171" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D171">
         <v>27000</v>
@@ -7758,10 +7758,10 @@
         <v>1</v>
       </c>
       <c r="H171" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="I171" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
@@ -7772,7 +7772,7 @@
         <v>431</v>
       </c>
       <c r="C172" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D172">
         <v>27000</v>
@@ -7784,10 +7784,10 @@
         <v>1</v>
       </c>
       <c r="H172" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="I172" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.25">
@@ -7798,7 +7798,7 @@
         <v>432</v>
       </c>
       <c r="C173" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D173">
         <v>27000</v>
@@ -7810,10 +7810,10 @@
         <v>1</v>
       </c>
       <c r="H173" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="I173" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.25">
@@ -7824,7 +7824,7 @@
         <v>433</v>
       </c>
       <c r="C174" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D174">
         <v>35000</v>
@@ -7836,10 +7836,10 @@
         <v>1</v>
       </c>
       <c r="H174" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="I174" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.25">
@@ -7850,7 +7850,7 @@
         <v>434</v>
       </c>
       <c r="C175" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D175">
         <v>35000</v>
@@ -7862,10 +7862,10 @@
         <v>1</v>
       </c>
       <c r="H175" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="I175" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.25">
@@ -7876,7 +7876,7 @@
         <v>435</v>
       </c>
       <c r="C176" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D176">
         <v>35000</v>
@@ -7888,10 +7888,10 @@
         <v>1</v>
       </c>
       <c r="H176" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="I176" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
@@ -7902,7 +7902,7 @@
         <v>436</v>
       </c>
       <c r="C177" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D177">
         <v>35000</v>
@@ -7914,10 +7914,10 @@
         <v>1</v>
       </c>
       <c r="H177" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="I177" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
@@ -7928,7 +7928,7 @@
         <v>437</v>
       </c>
       <c r="C178" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D178">
         <v>35000</v>
@@ -7940,10 +7940,10 @@
         <v>1</v>
       </c>
       <c r="H178" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="I178" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
@@ -7954,7 +7954,7 @@
         <v>438</v>
       </c>
       <c r="C179" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D179">
         <v>35000</v>
@@ -7966,10 +7966,10 @@
         <v>1</v>
       </c>
       <c r="H179" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="I179" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
@@ -7980,7 +7980,7 @@
         <v>439</v>
       </c>
       <c r="C180" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D180">
         <v>25000</v>
@@ -7992,10 +7992,10 @@
         <v>1</v>
       </c>
       <c r="H180" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="I180" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
@@ -8006,7 +8006,7 @@
         <v>440</v>
       </c>
       <c r="C181" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D181">
         <v>25000</v>
@@ -8018,10 +8018,10 @@
         <v>1</v>
       </c>
       <c r="H181" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="I181" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
@@ -8032,7 +8032,7 @@
         <v>441</v>
       </c>
       <c r="C182" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D182">
         <v>25000</v>
@@ -8044,10 +8044,10 @@
         <v>1</v>
       </c>
       <c r="H182" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="I182" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
@@ -8058,7 +8058,7 @@
         <v>442</v>
       </c>
       <c r="C183" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D183">
         <v>25000</v>
@@ -8070,10 +8070,10 @@
         <v>1</v>
       </c>
       <c r="H183" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="I183" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
@@ -8084,7 +8084,7 @@
         <v>443</v>
       </c>
       <c r="C184" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D184">
         <v>25000</v>
@@ -8096,10 +8096,10 @@
         <v>1</v>
       </c>
       <c r="H184" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="I184" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
@@ -8110,7 +8110,7 @@
         <v>444</v>
       </c>
       <c r="C185" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D185">
         <v>15000</v>
@@ -8122,10 +8122,10 @@
         <v>6</v>
       </c>
       <c r="H185" t="s">
+        <v>740</v>
+      </c>
+      <c r="I185" t="s">
         <v>741</v>
-      </c>
-      <c r="I185" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
@@ -8136,7 +8136,7 @@
         <v>445</v>
       </c>
       <c r="C186" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D186">
         <v>25000</v>
@@ -8148,10 +8148,10 @@
         <v>1</v>
       </c>
       <c r="H186" t="s">
+        <v>743</v>
+      </c>
+      <c r="I186" t="s">
         <v>744</v>
-      </c>
-      <c r="I186" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
@@ -8162,7 +8162,7 @@
         <v>446</v>
       </c>
       <c r="C187" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D187">
         <v>15000</v>
@@ -8174,10 +8174,10 @@
         <v>1</v>
       </c>
       <c r="H187" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="I187" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
@@ -8188,7 +8188,7 @@
         <v>447</v>
       </c>
       <c r="C188" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D188">
         <v>15000</v>
@@ -8200,10 +8200,10 @@
         <v>1</v>
       </c>
       <c r="H188" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="I188" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
@@ -8214,7 +8214,7 @@
         <v>448</v>
       </c>
       <c r="C189" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D189">
         <v>15000</v>
@@ -8226,10 +8226,10 @@
         <v>1</v>
       </c>
       <c r="H189" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="I189" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
@@ -8240,7 +8240,7 @@
         <v>449</v>
       </c>
       <c r="C190" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D190">
         <v>15000</v>
@@ -8252,10 +8252,10 @@
         <v>1</v>
       </c>
       <c r="H190" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="I190" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
   </sheetData>
@@ -12636,7 +12636,7 @@
         <v>118</v>
       </c>
       <c r="B1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C1">
         <v>1</v>
@@ -12650,7 +12650,7 @@
         <v>123</v>
       </c>
       <c r="B2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -12664,7 +12664,7 @@
         <v>128</v>
       </c>
       <c r="B3" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -12678,7 +12678,7 @@
         <v>133</v>
       </c>
       <c r="B4" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -12692,7 +12692,7 @@
         <v>138</v>
       </c>
       <c r="B5" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -12706,7 +12706,7 @@
         <v>143</v>
       </c>
       <c r="B6" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C6">
         <v>6</v>
@@ -12720,7 +12720,7 @@
         <v>148</v>
       </c>
       <c r="B7" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -12734,7 +12734,7 @@
         <v>153</v>
       </c>
       <c r="B8" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C8">
         <v>8</v>
@@ -12748,7 +12748,7 @@
         <v>158</v>
       </c>
       <c r="B9" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C9">
         <v>9</v>
@@ -12762,7 +12762,7 @@
         <v>163</v>
       </c>
       <c r="B10" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C10">
         <v>10</v>
@@ -12776,7 +12776,7 @@
         <v>168</v>
       </c>
       <c r="B11" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C11">
         <v>11</v>
@@ -12790,7 +12790,7 @@
         <v>173</v>
       </c>
       <c r="B12" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C12">
         <v>12</v>
@@ -12804,7 +12804,7 @@
         <v>178</v>
       </c>
       <c r="B13" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C13">
         <v>13</v>
@@ -12818,7 +12818,7 @@
         <v>183</v>
       </c>
       <c r="B14" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C14">
         <v>14</v>
@@ -12832,7 +12832,7 @@
         <v>188</v>
       </c>
       <c r="B15" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C15">
         <v>15</v>
@@ -12846,7 +12846,7 @@
         <v>193</v>
       </c>
       <c r="B16" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C16">
         <v>16</v>
@@ -12860,7 +12860,7 @@
         <v>198</v>
       </c>
       <c r="B17" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C17">
         <v>17</v>
@@ -12874,7 +12874,7 @@
         <v>203</v>
       </c>
       <c r="B18" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C18">
         <v>18</v>
@@ -12888,7 +12888,7 @@
         <v>208</v>
       </c>
       <c r="B19" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C19">
         <v>19</v>
@@ -12902,7 +12902,7 @@
         <v>213</v>
       </c>
       <c r="B20" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C20">
         <v>20</v>
